--- a/템플릿/토건 명세표 템플릿.xlsx
+++ b/템플릿/토건 명세표 템플릿.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\.shortcut-targets-by-id\1j04MMoet9_yHyMEheShb_L_xq-0Mij5h\3. 온결(신규법인)\ON260901-16101(백지혜, 장성욱, 여의도동 아파트 상속) 정우진\__평가서\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\내 드라이브\02.하이테크\온결(우진)\ON260902-3001(임근실 성남여수동 상속증여 토건) 정우진\__평가서\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{334BBA9A-239B-4A9D-B61D-26BF0B43E4DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50FE3616-FD54-4EE9-B04F-5C3CE9F2F223}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" tabRatio="724" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,9 +16,9 @@
     <sheet name="Sheet2" sheetId="4" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet2!$B$3:$J$54</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Sheet2'!$B$3:$K$54</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -35,9 +35,122 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="33">
+  <si>
+    <t>일련
+번호</t>
+  </si>
+  <si>
+    <t>소재지</t>
+  </si>
+  <si>
+    <t>지 번</t>
+  </si>
+  <si>
+    <t>지목 및
+용   도</t>
+  </si>
+  <si>
+    <t>용도지역
+및  구조</t>
+  </si>
+  <si>
+    <t>면  적  (㎡)</t>
+  </si>
+  <si>
+    <t>감 정 평 가 액</t>
+  </si>
+  <si>
+    <t>비 고</t>
+  </si>
+  <si>
+    <t>공 부</t>
+  </si>
+  <si>
+    <t>사 정</t>
+  </si>
+  <si>
+    <t>금액(원)</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>여수동</t>
+  </si>
+  <si>
+    <t>457</t>
+  </si>
+  <si>
+    <t>대</t>
+  </si>
+  <si>
+    <t>1종일주</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>가</t>
+  </si>
+  <si>
+    <t>제2종근린생활시</t>
+  </si>
+  <si>
+    <t>철근콘크리트구조</t>
+  </si>
+  <si>
+    <t>설(일반음식점)</t>
+  </si>
+  <si>
+    <t>1층</t>
+  </si>
+  <si>
+    <t>2층</t>
+  </si>
+  <si>
+    <t>3층</t>
+  </si>
+  <si>
+    <t>4층</t>
+  </si>
+  <si>
+    <t>계단,승강기탑</t>
+  </si>
+  <si>
+    <t>옥탑1층</t>
+  </si>
+  <si>
+    <t>합  계</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            (토지·건물)감정평가명세표</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>단가
+(원/㎡)</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>다가구주택</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1가구)</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>x 36/50</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="16">
+  <numFmts count="12">
     <numFmt numFmtId="42" formatCode="_-&quot;₩&quot;* #,##0_-;\-&quot;₩&quot;* #,##0_-;_-&quot;₩&quot;* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
@@ -49,11 +162,7 @@
     <numFmt numFmtId="181" formatCode="#,##0.0"/>
     <numFmt numFmtId="182" formatCode="#,##0.00##"/>
     <numFmt numFmtId="183" formatCode="#,##0.00_);[Red]\(#,##0.00\)"/>
-    <numFmt numFmtId="184" formatCode="#,##0.0_);[Red]\(#,##0.0\)"/>
-    <numFmt numFmtId="185" formatCode="#,##0.000_);[Red]\(#,##0.000\)"/>
-    <numFmt numFmtId="186" formatCode="#,##0.0000_);[Red]\(#,##0.0000\)"/>
-    <numFmt numFmtId="187" formatCode="mm&quot;월&quot;\ dd&quot;일&quot;"/>
-    <numFmt numFmtId="193" formatCode="&quot;₩&quot;#,##0"/>
+    <numFmt numFmtId="188" formatCode="&quot;₩&quot;#,##0"/>
   </numFmts>
   <fonts count="15" x14ac:knownFonts="1">
     <font>
@@ -395,172 +504,136 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="42" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="41" fontId="10" fillId="0" borderId="0" xfId="17" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="183" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="183" fontId="8" fillId="0" borderId="0" xfId="17" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="8" fillId="0" borderId="0" xfId="17" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="11" fillId="0" borderId="3" xfId="17" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="11" fillId="0" borderId="3" xfId="17" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="183" fontId="11" fillId="0" borderId="3" xfId="17" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="11" fillId="0" borderId="3" xfId="17" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="12" fillId="0" borderId="3" xfId="20" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="183" fontId="11" fillId="0" borderId="4" xfId="17" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="11" fillId="0" borderId="4" xfId="17" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="12" fillId="0" borderId="4" xfId="20" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="14" fillId="0" borderId="0" xfId="17" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="17" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="12" fillId="0" borderId="9" xfId="17" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="12" fillId="0" borderId="16" xfId="17" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="183" fontId="11" fillId="3" borderId="3" xfId="17" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="188" fontId="13" fillId="3" borderId="9" xfId="20" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="12" fillId="3" borderId="9" xfId="17" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="8" fillId="0" borderId="0" xfId="17" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="41" fontId="10" fillId="0" borderId="0" xfId="17" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="183" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="183" fontId="8" fillId="0" borderId="0" xfId="17" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="8" fillId="0" borderId="0" xfId="17" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="8" fillId="0" borderId="0" xfId="17" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="11" fillId="0" borderId="3" xfId="17" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="11" fillId="0" borderId="3" xfId="17" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="183" fontId="11" fillId="0" borderId="3" xfId="17" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="11" fillId="0" borderId="3" xfId="17" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="186" fontId="11" fillId="0" borderId="3" xfId="17" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="185" fontId="11" fillId="0" borderId="3" xfId="17" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="187" fontId="11" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="184" fontId="11" fillId="0" borderId="3" xfId="17" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="184" fontId="11" fillId="0" borderId="3" xfId="17" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="186" fontId="11" fillId="0" borderId="3" xfId="17" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="11" fillId="0" borderId="3" xfId="17" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="183" fontId="11" fillId="0" borderId="3" xfId="17" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="11" fillId="0" borderId="3" xfId="17" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="12" fillId="0" borderId="3" xfId="20" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="183" fontId="11" fillId="0" borderId="4" xfId="17" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="11" fillId="0" borderId="4" xfId="17" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="12" fillId="0" borderId="4" xfId="20" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="14" fillId="0" borderId="0" xfId="17" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="17" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="17" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="11" fillId="0" borderId="0" xfId="17" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="183" fontId="11" fillId="3" borderId="9" xfId="17" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="11" fillId="0" borderId="3" xfId="17" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="12" fillId="0" borderId="9" xfId="17" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="12" fillId="0" borderId="16" xfId="17" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="183" fontId="11" fillId="3" borderId="3" xfId="17" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="193" fontId="13" fillId="3" borderId="9" xfId="20" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="12" fillId="3" borderId="9" xfId="17" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="11" fillId="0" borderId="9" xfId="17" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -610,7 +683,7 @@
       <xdr:rowOff>134235</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>8</xdr:col>
+      <xdr:col>9</xdr:col>
       <xdr:colOff>881658</xdr:colOff>
       <xdr:row>54</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
@@ -701,101 +774,6 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>36420</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>126092</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>207683</xdr:colOff>
-      <xdr:row>39</xdr:row>
-      <xdr:rowOff>145677</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="3" name="자유형: 도형 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7D6B3548-6AAD-49DD-9A53-6814648E86FE}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="6792820" y="6596742"/>
-          <a:ext cx="171263" cy="908585"/>
-        </a:xfrm>
-        <a:custGeom>
-          <a:avLst/>
-          <a:gdLst>
-            <a:gd name="csX0" fmla="*/ 0 w 239485"/>
-            <a:gd name="csY0" fmla="*/ 0 h 656771"/>
-            <a:gd name="csX1" fmla="*/ 239485 w 239485"/>
-            <a:gd name="csY1" fmla="*/ 0 h 656771"/>
-            <a:gd name="csX2" fmla="*/ 239485 w 239485"/>
-            <a:gd name="csY2" fmla="*/ 656771 h 656771"/>
-            <a:gd name="csX3" fmla="*/ 10885 w 239485"/>
-            <a:gd name="csY3" fmla="*/ 656771 h 656771"/>
-          </a:gdLst>
-          <a:ahLst/>
-          <a:cxnLst>
-            <a:cxn ang="0">
-              <a:pos x="csX0" y="csY0"/>
-            </a:cxn>
-            <a:cxn ang="0">
-              <a:pos x="csX1" y="csY1"/>
-            </a:cxn>
-            <a:cxn ang="0">
-              <a:pos x="csX2" y="csY2"/>
-            </a:cxn>
-            <a:cxn ang="0">
-              <a:pos x="csX3" y="csY3"/>
-            </a:cxn>
-          </a:cxnLst>
-          <a:rect l="l" t="t" r="r" b="b"/>
-          <a:pathLst>
-            <a:path w="239485" h="656771">
-              <a:moveTo>
-                <a:pt x="0" y="0"/>
-              </a:moveTo>
-              <a:lnTo>
-                <a:pt x="239485" y="0"/>
-              </a:lnTo>
-              <a:lnTo>
-                <a:pt x="239485" y="656771"/>
-              </a:lnTo>
-              <a:lnTo>
-                <a:pt x="10885" y="656771"/>
-              </a:lnTo>
-            </a:path>
-          </a:pathLst>
-        </a:custGeom>
-        <a:noFill/>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:srgbClr val="000000"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:round/>
-        </a:ln>
-        <a:effectLst/>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr rtlCol="0" anchor="ctr"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>225280</xdr:colOff>
       <xdr:row>2</xdr:row>
@@ -820,8 +798,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="225280" y="427183"/>
-          <a:ext cx="1702811" cy="1616361"/>
+          <a:off x="225280" y="415638"/>
+          <a:ext cx="1640136" cy="1621308"/>
           <a:chOff x="361950" y="806450"/>
           <a:chExt cx="1295400" cy="1217312"/>
         </a:xfrm>
@@ -1034,7 +1012,7 @@
       <xdr:rowOff>76361</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>9</xdr:col>
+      <xdr:col>10</xdr:col>
       <xdr:colOff>803017</xdr:colOff>
       <xdr:row>5</xdr:row>
       <xdr:rowOff>76361</xdr:rowOff>
@@ -1402,691 +1380,706 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B3:J55"/>
+  <dimension ref="B3:K55"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="3.5" style="6" customWidth="1"/>
-    <col min="2" max="2" width="6.75" style="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15" style="6" customWidth="1"/>
-    <col min="4" max="5" width="11" style="6" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="22.5" style="6" customWidth="1"/>
-    <col min="7" max="7" width="17.25" style="6" customWidth="1"/>
-    <col min="8" max="8" width="9.08203125" style="6" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="24.9140625" style="6" customWidth="1"/>
-    <col min="10" max="10" width="11.1640625" style="6" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="6.5" style="6" customWidth="1"/>
-    <col min="12" max="16384" width="8.6640625" style="6"/>
+    <col min="1" max="1" width="3.5" style="2" customWidth="1"/>
+    <col min="2" max="2" width="6.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15" style="2" customWidth="1"/>
+    <col min="4" max="4" width="11" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="22.5" style="2" customWidth="1"/>
+    <col min="7" max="7" width="13.9140625" style="2" customWidth="1"/>
+    <col min="8" max="8" width="13.83203125" style="2" customWidth="1"/>
+    <col min="9" max="9" width="14.83203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="24.9140625" style="2" customWidth="1"/>
+    <col min="11" max="11" width="13.33203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="6.5" style="2" customWidth="1"/>
+    <col min="13" max="16384" width="8.6640625" style="2"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:10" ht="52.5" x14ac:dyDescent="1.25">
-      <c r="C3" s="38"/>
-      <c r="D3" s="38"/>
-      <c r="E3" s="38"/>
-      <c r="F3" s="38"/>
-      <c r="G3" s="38"/>
-      <c r="H3" s="38"/>
-      <c r="I3" s="38"/>
-      <c r="J3" s="38"/>
-    </row>
-    <row r="4" spans="2:10" ht="47.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B4" s="37" t="inlineStr">
-        <is>
-          <t>            (토지·건물)감정평가명세표</t>
-        </is>
-      </c>
-      <c r="G4" s="8"/>
-    </row>
-    <row r="5" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B5" s="7"/>
-      <c r="G5" s="8"/>
-    </row>
-    <row r="6" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B6" s="7"/>
-      <c r="G6" s="8"/>
-    </row>
-    <row r="7" spans="2:10" ht="15.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B7" s="9"/>
-      <c r="C7" s="10"/>
-      <c r="D7" s="9"/>
-      <c r="E7" s="10"/>
-      <c r="F7" s="10"/>
-      <c r="G7" s="11"/>
-      <c r="H7" s="12"/>
-      <c r="I7" s="13"/>
-      <c r="J7" s="13"/>
-    </row>
-    <row r="8" spans="2:10" ht="24.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B8" s="39" t="inlineStr">
-        <is>
-          <t>일련
-번호</t>
-        </is>
-      </c>
-      <c r="C8" s="1" t="inlineStr">
-        <is>
-          <t>소재지</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="inlineStr">
-        <is>
-          <t>지 번</t>
-        </is>
-      </c>
-      <c r="E8" s="1" t="inlineStr">
-        <is>
-          <t>지목 및
-용   도</t>
-        </is>
-      </c>
-      <c r="F8" s="1" t="inlineStr">
-        <is>
-          <t>용도지역
-및  구조</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>면  적  (㎡)</t>
-        </is>
-      </c>
-      <c r="H8" s="3"/>
-      <c r="I8" s="4" t="inlineStr">
-        <is>
-          <t>감 정 평 가 액</t>
-        </is>
-      </c>
-      <c r="J8" s="40" t="inlineStr">
-        <is>
-          <t>비 고</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" spans="2:10" ht="24.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="B9" s="41"/>
-      <c r="C9" s="5"/>
-      <c r="D9" s="5"/>
-      <c r="E9" s="5"/>
-      <c r="F9" s="5"/>
-      <c r="G9" s="4" t="inlineStr">
-        <is>
-          <t>공 부</t>
-        </is>
-      </c>
-      <c r="H9" s="4" t="inlineStr">
-        <is>
-          <t>사 정</t>
-        </is>
-      </c>
-      <c r="I9" s="4" t="inlineStr">
-        <is>
-          <t>금액(원)</t>
-        </is>
-      </c>
-      <c r="J9" s="42"/>
-    </row>
-    <row r="10" spans="2:10" ht="23" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B10" s="43"/>
-      <c r="C10" s="14"/>
-      <c r="D10" s="15"/>
-      <c r="E10" s="15"/>
-      <c r="F10" s="15"/>
-      <c r="G10" s="15"/>
-      <c r="H10" s="15"/>
-      <c r="I10" s="15"/>
-      <c r="J10" s="44"/>
-    </row>
-    <row r="11" spans="2:10" ht="23" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B11" s="43" t="inlineStr">
+    <row r="3" spans="2:11" ht="52.5" x14ac:dyDescent="1.25">
+      <c r="C3" s="22"/>
+      <c r="D3" s="22"/>
+      <c r="E3" s="22"/>
+      <c r="F3" s="22"/>
+      <c r="G3" s="22"/>
+      <c r="H3" s="22"/>
+      <c r="I3" s="22"/>
+      <c r="J3" s="22"/>
+      <c r="K3" s="22"/>
+    </row>
+    <row r="4" spans="2:11" ht="47.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B4" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="G4" s="4"/>
+    </row>
+    <row r="5" spans="2:11" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B5" s="3"/>
+      <c r="G5" s="4"/>
+    </row>
+    <row r="6" spans="2:11" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B6" s="3"/>
+      <c r="G6" s="4"/>
+    </row>
+    <row r="7" spans="2:11" ht="15.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B7" s="5"/>
+      <c r="C7" s="6"/>
+      <c r="D7" s="5"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="6"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="8"/>
+      <c r="I7" s="8"/>
+      <c r="J7" s="35"/>
+      <c r="K7" s="35"/>
+    </row>
+    <row r="8" spans="2:11" ht="24.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B8" s="36" t="s">
+        <v>0</v>
+      </c>
+      <c r="C8" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="D8" s="38" t="s">
+        <v>2</v>
+      </c>
+      <c r="E8" s="38" t="s">
+        <v>3</v>
+      </c>
+      <c r="F8" s="38" t="s">
+        <v>4</v>
+      </c>
+      <c r="G8" s="40" t="s">
+        <v>5</v>
+      </c>
+      <c r="H8" s="41"/>
+      <c r="I8" s="40" t="s">
+        <v>6</v>
+      </c>
+      <c r="J8" s="41"/>
+      <c r="K8" s="42" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="2:11" ht="48" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
+      <c r="B9" s="37"/>
+      <c r="C9" s="39"/>
+      <c r="D9" s="39"/>
+      <c r="E9" s="39"/>
+      <c r="F9" s="39"/>
+      <c r="G9" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="K9" s="43"/>
+    </row>
+    <row r="11" spans="2:11" ht="21.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B11" s="23" t="inlineStr">
         <is>
           <t>{{명세_기호}}</t>
         </is>
       </c>
-      <c r="C11" s="14" t="inlineStr">
+      <c r="C11" s="9" t="inlineStr">
         <is>
           <t>{{명세_소재지}}</t>
         </is>
       </c>
-      <c r="D11" s="15" t="inlineStr">
+      <c r="D11" s="10" t="inlineStr">
         <is>
           <t>{{명세_지번}}</t>
         </is>
       </c>
-      <c r="E11" s="15" t="inlineStr">
+      <c r="E11" s="10" t="inlineStr">
         <is>
           <t>{{명세_지목용도}}</t>
         </is>
       </c>
-      <c r="F11" s="14" t="inlineStr">
+      <c r="F11" s="9" t="inlineStr">
         <is>
           <t>{{명세_지역구조}}</t>
         </is>
       </c>
-      <c r="G11" s="16" t="inlineStr">
+      <c r="G11" s="11" t="inlineStr">
         <is>
           <t>{{명세_공부면적}}</t>
         </is>
       </c>
-      <c r="H11" s="16" t="inlineStr">
+      <c r="H11" s="11" t="inlineStr">
         <is>
           <t>{{명세_사정면적}}</t>
         </is>
       </c>
-      <c r="I11" s="17" t="inlineStr">
+      <c r="I11" s="45" t="inlineStr">
         <is>
-          <t>{{명세_평가액}}</t>
+          <t>{{명세_단가}}</t>
         </is>
       </c>
-      <c r="J11" s="44" t="inlineStr">
+      <c r="J11" s="12">
+        <f>+I11*H11</f>
+      </c>
+      <c r="K11" s="24" t="inlineStr">
         <is>
           <t>{{명세_비고}}</t>
         </is>
       </c>
     </row>
-    <row r="12" spans="2:10" ht="23" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B12" s="43"/>
-      <c r="C12" s="14"/>
-      <c r="D12" s="15"/>
-      <c r="E12" s="15"/>
-      <c r="F12" s="14"/>
-      <c r="G12" s="18"/>
-      <c r="H12" s="19"/>
-      <c r="I12" s="17"/>
-      <c r="J12" s="44"/>
-    </row>
-    <row r="13" spans="2:10" ht="23" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B13" s="43"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="15"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="14"/>
-      <c r="G13" s="20"/>
-      <c r="H13" s="19"/>
-      <c r="I13" s="17"/>
-      <c r="J13" s="44"/>
-    </row>
-    <row r="14" spans="2:10" ht="23" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B14" s="43"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="15"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="15"/>
-      <c r="G14" s="20"/>
-      <c r="H14" s="19"/>
-      <c r="I14" s="17"/>
-      <c r="J14" s="44"/>
-    </row>
-    <row r="15" spans="2:10" ht="23" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B15" s="43"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="15"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="45"/>
-      <c r="G15" s="20"/>
-      <c r="H15" s="19"/>
-      <c r="I15" s="17"/>
-      <c r="J15" s="44"/>
-    </row>
-    <row r="16" spans="2:10" ht="23" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B16" s="43"/>
-      <c r="C16" s="14"/>
-      <c r="D16" s="15"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="15"/>
-      <c r="G16" s="20"/>
-      <c r="H16" s="19"/>
-      <c r="I16" s="17"/>
-      <c r="J16" s="44"/>
-    </row>
-    <row r="17" spans="2:10" ht="23" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B17" s="43"/>
-      <c r="C17" s="14"/>
-      <c r="D17" s="14"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="14"/>
-      <c r="G17" s="18"/>
-      <c r="H17" s="20"/>
-      <c r="I17" s="17"/>
-      <c r="J17" s="44"/>
-    </row>
-    <row r="18" spans="2:10" ht="23" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B18" s="43"/>
-      <c r="C18" s="14"/>
-      <c r="D18" s="14"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="14"/>
-      <c r="G18" s="21"/>
-      <c r="H18" s="20"/>
-      <c r="I18" s="17"/>
-      <c r="J18" s="44"/>
-    </row>
-    <row r="19" spans="2:10" ht="23" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B19" s="43"/>
-      <c r="C19" s="14"/>
-      <c r="D19" s="14"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="14"/>
-      <c r="G19" s="21"/>
-      <c r="H19" s="20"/>
-      <c r="I19" s="17"/>
-      <c r="J19" s="44"/>
-    </row>
-    <row r="20" spans="2:10" ht="23" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B20" s="43"/>
-      <c r="C20" s="14"/>
-      <c r="D20" s="14"/>
-      <c r="E20" s="14"/>
-      <c r="F20" s="14"/>
-      <c r="G20" s="21"/>
-      <c r="H20" s="20"/>
-      <c r="I20" s="17"/>
-      <c r="J20" s="44"/>
-    </row>
-    <row r="21" spans="2:10" ht="23" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B21" s="43"/>
-      <c r="C21" s="14"/>
-      <c r="D21" s="14"/>
-      <c r="E21" s="14"/>
-      <c r="F21" s="14"/>
-      <c r="G21" s="21"/>
-      <c r="H21" s="20"/>
-      <c r="I21" s="17"/>
-      <c r="J21" s="44"/>
-    </row>
-    <row r="22" spans="2:10" ht="23" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B22" s="43"/>
-      <c r="C22" s="22"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="14"/>
-      <c r="G22" s="21"/>
-      <c r="H22" s="20"/>
-      <c r="I22" s="17"/>
-      <c r="J22" s="44"/>
-    </row>
-    <row r="23" spans="2:10" ht="23" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B23" s="43"/>
-      <c r="C23" s="22"/>
-      <c r="D23" s="14"/>
-      <c r="E23" s="14"/>
-      <c r="F23" s="14"/>
-      <c r="G23" s="21"/>
-      <c r="H23" s="20"/>
-      <c r="I23" s="17"/>
-      <c r="J23" s="44"/>
-    </row>
-    <row r="24" spans="2:10" ht="23" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B24" s="43"/>
-      <c r="C24" s="14"/>
-      <c r="D24" s="14"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="21"/>
-      <c r="H24" s="20"/>
-      <c r="I24" s="17"/>
-      <c r="J24" s="44"/>
-    </row>
-    <row r="25" spans="2:10" ht="23" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B25" s="46"/>
-      <c r="C25" s="14"/>
-      <c r="D25" s="23"/>
-      <c r="E25" s="14"/>
-      <c r="F25" s="14"/>
-      <c r="G25" s="24"/>
-      <c r="H25" s="20"/>
-      <c r="I25" s="17"/>
-      <c r="J25" s="44"/>
-    </row>
-    <row r="26" spans="2:10" ht="23" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B26" s="46"/>
-      <c r="C26" s="14"/>
-      <c r="D26" s="23"/>
-      <c r="E26" s="14"/>
-      <c r="F26" s="14"/>
-      <c r="G26" s="24"/>
-      <c r="H26" s="20"/>
-      <c r="I26" s="17"/>
-      <c r="J26" s="44"/>
-    </row>
-    <row r="27" spans="2:10" ht="23" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B27" s="46"/>
-      <c r="C27" s="14"/>
-      <c r="D27" s="23"/>
-      <c r="E27" s="14"/>
-      <c r="F27" s="14"/>
-      <c r="G27" s="24"/>
-      <c r="H27" s="20"/>
-      <c r="I27" s="17"/>
-      <c r="J27" s="44"/>
-    </row>
-    <row r="28" spans="2:10" ht="23" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B28" s="46"/>
-      <c r="C28" s="14"/>
-      <c r="D28" s="23"/>
-      <c r="E28" s="14"/>
-      <c r="F28" s="14"/>
-      <c r="G28" s="24"/>
-      <c r="H28" s="20"/>
-      <c r="I28" s="17"/>
-      <c r="J28" s="44"/>
-    </row>
-    <row r="29" spans="2:10" ht="23" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B29" s="46"/>
-      <c r="C29" s="14"/>
-      <c r="D29" s="23"/>
-      <c r="E29" s="14"/>
-      <c r="F29" s="14"/>
-      <c r="G29" s="24"/>
-      <c r="H29" s="20"/>
-      <c r="I29" s="17"/>
-      <c r="J29" s="44"/>
-    </row>
-    <row r="30" spans="2:10" ht="23" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B30" s="46"/>
-      <c r="C30" s="14"/>
-      <c r="D30" s="23"/>
-      <c r="E30" s="14"/>
-      <c r="F30" s="14"/>
-      <c r="G30" s="24"/>
-      <c r="H30" s="20"/>
-      <c r="I30" s="17"/>
-      <c r="J30" s="44"/>
-    </row>
-    <row r="31" spans="2:10" ht="23" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B31" s="43"/>
-      <c r="C31" s="14"/>
-      <c r="D31" s="14"/>
-      <c r="E31" s="14"/>
-      <c r="F31" s="14"/>
-      <c r="G31" s="16"/>
-      <c r="H31" s="18"/>
-      <c r="I31" s="17"/>
-      <c r="J31" s="44"/>
-    </row>
-    <row r="32" spans="2:10" ht="23" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B32" s="43"/>
-      <c r="C32" s="14"/>
-      <c r="D32" s="14"/>
-      <c r="E32" s="14"/>
-      <c r="F32" s="14"/>
-      <c r="G32" s="16"/>
-      <c r="H32" s="18"/>
-      <c r="I32" s="17"/>
-      <c r="J32" s="44"/>
-    </row>
-    <row r="33" spans="2:10" ht="23" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B33" s="43"/>
-      <c r="C33" s="14"/>
-      <c r="D33" s="14"/>
-      <c r="E33" s="14"/>
-      <c r="F33" s="14"/>
-      <c r="G33" s="16"/>
-      <c r="H33" s="18"/>
-      <c r="I33" s="17"/>
-      <c r="J33" s="44"/>
-    </row>
-    <row r="34" spans="2:10" ht="23" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B34" s="43"/>
-      <c r="C34" s="14"/>
-      <c r="D34" s="14"/>
-      <c r="E34" s="14"/>
-      <c r="F34" s="14"/>
-      <c r="G34" s="18"/>
-      <c r="H34" s="18"/>
-      <c r="I34" s="17"/>
-      <c r="J34" s="47"/>
-    </row>
-    <row r="35" spans="2:10" ht="23" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B35" s="43"/>
-      <c r="C35" s="14"/>
-      <c r="D35" s="14"/>
-      <c r="E35" s="14"/>
-      <c r="F35" s="14"/>
-      <c r="G35" s="16"/>
-      <c r="H35" s="18"/>
-      <c r="I35" s="17"/>
-      <c r="J35" s="47"/>
-    </row>
-    <row r="36" spans="2:10" ht="23" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B36" s="43"/>
-      <c r="C36" s="14"/>
-      <c r="D36" s="14"/>
-      <c r="E36" s="14"/>
-      <c r="F36" s="14"/>
-      <c r="G36" s="16"/>
-      <c r="H36" s="18"/>
-      <c r="I36" s="17"/>
-      <c r="J36" s="47"/>
-    </row>
-    <row r="37" spans="2:10" ht="23" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B37" s="43"/>
-      <c r="C37" s="14"/>
-      <c r="D37" s="14"/>
-      <c r="E37" s="14"/>
-      <c r="F37" s="14"/>
-      <c r="G37" s="16"/>
-      <c r="H37" s="18"/>
-      <c r="I37" s="17"/>
-      <c r="J37" s="47"/>
-    </row>
-    <row r="38" spans="2:10" ht="23" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B38" s="43"/>
-      <c r="C38" s="14"/>
-      <c r="D38" s="14"/>
-      <c r="E38" s="14"/>
-      <c r="F38" s="14"/>
-      <c r="G38" s="16"/>
-      <c r="H38" s="18"/>
-      <c r="I38" s="48"/>
-      <c r="J38" s="47"/>
-    </row>
-    <row r="39" spans="2:10" ht="23" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B39" s="43"/>
-      <c r="C39" s="14"/>
-      <c r="D39" s="14"/>
-      <c r="E39" s="14"/>
-      <c r="F39" s="14"/>
-      <c r="G39" s="18"/>
-      <c r="H39" s="18"/>
-      <c r="I39" s="49"/>
-      <c r="J39" s="44"/>
-    </row>
-    <row r="40" spans="2:10" ht="23" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B40" s="43"/>
-      <c r="C40" s="14"/>
-      <c r="D40" s="50"/>
-      <c r="E40" s="15"/>
-      <c r="F40" s="14"/>
-      <c r="G40" s="16"/>
-      <c r="H40" s="18"/>
-      <c r="I40" s="17"/>
-      <c r="J40" s="44"/>
-    </row>
-    <row r="41" spans="2:10" ht="23" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B41" s="43"/>
-      <c r="C41" s="14"/>
-      <c r="D41" s="15"/>
-      <c r="E41" s="15"/>
-      <c r="F41" s="14"/>
-      <c r="G41" s="24"/>
-      <c r="H41" s="21"/>
-      <c r="I41" s="17"/>
-      <c r="J41" s="44"/>
-    </row>
-    <row r="42" spans="2:10" ht="23" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B42" s="43"/>
-      <c r="C42" s="14"/>
-      <c r="D42" s="15"/>
-      <c r="E42" s="14"/>
-      <c r="F42" s="14"/>
-      <c r="G42" s="14"/>
-      <c r="H42" s="14"/>
-      <c r="I42" s="14"/>
-      <c r="J42" s="44"/>
-    </row>
-    <row r="43" spans="2:10" ht="23" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B43" s="43"/>
-      <c r="C43" s="14"/>
-      <c r="D43" s="15"/>
-      <c r="E43" s="14"/>
-      <c r="F43" s="14"/>
-      <c r="G43" s="14"/>
-      <c r="H43" s="14"/>
-      <c r="I43" s="14"/>
-      <c r="J43" s="44"/>
-    </row>
-    <row r="44" spans="2:10" ht="23" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B44" s="43"/>
-      <c r="C44" s="14"/>
-      <c r="D44" s="15"/>
-      <c r="E44" s="14"/>
-      <c r="F44" s="14"/>
-      <c r="G44" s="14"/>
-      <c r="H44" s="14"/>
-      <c r="I44" s="14"/>
-      <c r="J44" s="44"/>
-    </row>
-    <row r="45" spans="2:10" ht="23" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B45" s="43"/>
-      <c r="C45" s="14"/>
-      <c r="D45" s="15"/>
-      <c r="E45" s="14"/>
-      <c r="F45" s="14"/>
-      <c r="G45" s="14"/>
-      <c r="H45" s="14"/>
-      <c r="I45" s="14"/>
-      <c r="J45" s="44"/>
-    </row>
-    <row r="46" spans="2:10" ht="23" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B46" s="43"/>
-      <c r="C46" s="14"/>
-      <c r="D46" s="14"/>
-      <c r="E46" s="14"/>
-      <c r="F46" s="26"/>
-      <c r="G46" s="27"/>
-      <c r="H46" s="28"/>
-      <c r="I46" s="29"/>
-      <c r="J46" s="51"/>
-    </row>
-    <row r="47" spans="2:10" ht="23" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B47" s="43"/>
-      <c r="C47" s="14"/>
-      <c r="D47" s="14"/>
-      <c r="E47" s="14"/>
-      <c r="F47" s="26"/>
-      <c r="G47" s="27"/>
-      <c r="H47" s="28"/>
-      <c r="I47" s="29"/>
-      <c r="J47" s="51"/>
-    </row>
-    <row r="48" spans="2:10" ht="23" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B48" s="43"/>
-      <c r="C48" s="14"/>
-      <c r="D48" s="14"/>
-      <c r="E48" s="14"/>
-      <c r="F48" s="26"/>
-      <c r="G48" s="27"/>
-      <c r="H48" s="28"/>
-      <c r="I48" s="29"/>
-      <c r="J48" s="51"/>
-    </row>
-    <row r="49" spans="2:10" ht="23" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B49" s="43"/>
-      <c r="C49" s="14"/>
-      <c r="D49" s="14"/>
-      <c r="E49" s="14"/>
-      <c r="F49" s="26"/>
-      <c r="G49" s="27"/>
-      <c r="H49" s="28"/>
-      <c r="I49" s="29"/>
-      <c r="J49" s="51"/>
-    </row>
-    <row r="50" spans="2:10" ht="23" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B50" s="55"/>
-      <c r="C50" s="56" t="inlineStr">
-        <is>
-          <t>합  계</t>
-        </is>
-      </c>
-      <c r="D50" s="57"/>
-      <c r="E50" s="57"/>
-      <c r="F50" s="57"/>
-      <c r="G50" s="58"/>
-      <c r="H50" s="58"/>
-      <c r="I50" s="59">
-        <f>SUM(I11:I45)</f>
-        <v>1400000000</v>
-      </c>
-      <c r="J50" s="60"/>
-    </row>
-    <row r="51" spans="2:10" ht="23" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B51" s="46"/>
-      <c r="C51" s="14"/>
-      <c r="D51" s="14"/>
-      <c r="E51" s="14"/>
-      <c r="F51" s="14"/>
-      <c r="G51" s="30"/>
-      <c r="H51" s="31"/>
-      <c r="I51" s="32"/>
-      <c r="J51" s="52"/>
-    </row>
-    <row r="52" spans="2:10" ht="23" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B52" s="46"/>
-      <c r="C52" s="14"/>
-      <c r="D52" s="14"/>
-      <c r="E52" s="14"/>
-      <c r="F52" s="14"/>
-      <c r="G52" s="30"/>
-      <c r="H52" s="31"/>
-      <c r="I52" s="32"/>
-      <c r="J52" s="52"/>
-    </row>
-    <row r="53" spans="2:10" ht="23" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B53" s="46"/>
-      <c r="C53" s="14"/>
-      <c r="D53" s="14"/>
-      <c r="E53" s="14"/>
-      <c r="F53" s="14"/>
-      <c r="G53" s="30"/>
-      <c r="H53" s="31"/>
-      <c r="I53" s="32"/>
-      <c r="J53" s="52"/>
-    </row>
-    <row r="54" spans="2:10" ht="23" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B54" s="53"/>
-      <c r="C54" s="33"/>
-      <c r="D54" s="33"/>
-      <c r="E54" s="33"/>
-      <c r="F54" s="33"/>
-      <c r="G54" s="34"/>
-      <c r="H54" s="35"/>
-      <c r="I54" s="36"/>
-      <c r="J54" s="54"/>
-    </row>
-    <row r="55" spans="2:10" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="B55" s="25"/>
-      <c r="C55" s="25"/>
-      <c r="D55" s="25"/>
-      <c r="E55" s="25"/>
-      <c r="F55" s="25"/>
-      <c r="G55" s="25"/>
-      <c r="H55" s="25"/>
-      <c r="I55" s="25"/>
-      <c r="J55" s="25"/>
+    <row r="12" spans="2:11" ht="21.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B12" s="23"/>
+      <c r="C12" s="9"/>
+      <c r="D12" s="10"/>
+      <c r="E12" s="10"/>
+      <c r="F12" s="9"/>
+      <c r="G12" s="11"/>
+      <c r="H12" s="11"/>
+      <c r="I12" s="11"/>
+      <c r="J12" s="12"/>
+      <c r="K12" s="24"/>
+    </row>
+    <row r="13" spans="2:11" ht="21.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B13" s="23"/>
+      <c r="C13" s="9"/>
+      <c r="D13" s="10"/>
+      <c r="E13" s="10"/>
+      <c r="F13" s="9"/>
+      <c r="G13" s="11"/>
+      <c r="H13" s="11"/>
+      <c r="I13" s="45"/>
+      <c r="J13" s="12"/>
+      <c r="K13" s="24"/>
+    </row>
+    <row r="14" spans="2:11" ht="21.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B14" s="23"/>
+      <c r="C14" s="9"/>
+      <c r="D14" s="10"/>
+      <c r="E14" s="10"/>
+      <c r="F14" s="9"/>
+      <c r="G14" s="11"/>
+      <c r="H14" s="11"/>
+      <c r="I14" s="45"/>
+      <c r="J14" s="12"/>
+      <c r="K14" s="24"/>
+    </row>
+    <row r="15" spans="2:11" ht="21.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B15" s="23"/>
+      <c r="C15" s="9"/>
+      <c r="D15" s="10"/>
+      <c r="E15" s="10"/>
+      <c r="F15" s="9"/>
+      <c r="G15" s="11"/>
+      <c r="H15" s="11"/>
+      <c r="I15" s="45"/>
+      <c r="J15" s="12"/>
+      <c r="K15" s="46"/>
+    </row>
+    <row r="16" spans="2:11" ht="21.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B16" s="23"/>
+      <c r="C16" s="9"/>
+      <c r="D16" s="10"/>
+      <c r="E16" s="10"/>
+      <c r="F16" s="9"/>
+      <c r="G16" s="11"/>
+      <c r="H16" s="11"/>
+      <c r="I16" s="45"/>
+      <c r="J16" s="12"/>
+      <c r="K16" s="24"/>
+    </row>
+    <row r="17" spans="2:11" ht="21.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B17" s="23"/>
+      <c r="C17" s="9"/>
+      <c r="D17" s="10"/>
+      <c r="E17" s="10"/>
+      <c r="F17" s="9"/>
+      <c r="G17" s="11"/>
+      <c r="H17" s="11"/>
+      <c r="I17" s="45"/>
+      <c r="J17" s="12"/>
+      <c r="K17" s="24"/>
+    </row>
+    <row r="18" spans="2:11" ht="21.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B18" s="23"/>
+      <c r="C18" s="9"/>
+      <c r="D18" s="10"/>
+      <c r="E18" s="10"/>
+      <c r="F18" s="9"/>
+      <c r="G18" s="11"/>
+      <c r="H18" s="11"/>
+      <c r="I18" s="45"/>
+      <c r="J18" s="12"/>
+      <c r="K18" s="24"/>
+    </row>
+    <row r="19" spans="2:11" ht="21.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B19" s="23"/>
+      <c r="C19" s="9"/>
+      <c r="D19" s="10"/>
+      <c r="E19" s="10"/>
+      <c r="F19" s="9"/>
+      <c r="G19" s="11"/>
+      <c r="H19" s="11"/>
+      <c r="I19" s="45"/>
+      <c r="J19" s="12"/>
+      <c r="K19" s="46"/>
+    </row>
+    <row r="20" spans="2:11" ht="21.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B20" s="23"/>
+      <c r="C20" s="9"/>
+      <c r="D20" s="10"/>
+      <c r="E20" s="10"/>
+      <c r="F20" s="9"/>
+      <c r="G20" s="11"/>
+      <c r="H20" s="11"/>
+      <c r="I20" s="45"/>
+      <c r="J20" s="12"/>
+      <c r="K20" s="24"/>
+    </row>
+    <row r="21" spans="2:11" ht="21.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B21" s="23"/>
+      <c r="C21" s="9"/>
+      <c r="D21" s="10"/>
+      <c r="E21" s="10"/>
+      <c r="F21" s="9"/>
+      <c r="G21" s="11"/>
+      <c r="H21" s="11"/>
+      <c r="I21" s="45"/>
+      <c r="J21" s="12"/>
+      <c r="K21" s="24"/>
+    </row>
+    <row r="22" spans="2:11" ht="21.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B22" s="23"/>
+      <c r="C22" s="9"/>
+      <c r="D22" s="10"/>
+      <c r="E22" s="10"/>
+      <c r="F22" s="9"/>
+      <c r="G22" s="11"/>
+      <c r="H22" s="11"/>
+      <c r="I22" s="45"/>
+      <c r="J22" s="12"/>
+      <c r="K22" s="24"/>
+    </row>
+    <row r="23" spans="2:11" ht="21.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B23" s="23"/>
+      <c r="C23" s="9"/>
+      <c r="D23" s="10"/>
+      <c r="E23" s="10"/>
+      <c r="F23" s="9"/>
+      <c r="G23" s="11"/>
+      <c r="H23" s="11"/>
+      <c r="I23" s="45"/>
+      <c r="J23" s="12"/>
+      <c r="K23" s="46"/>
+    </row>
+    <row r="24" spans="2:11" ht="21.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B24" s="23"/>
+      <c r="C24" s="9"/>
+      <c r="D24" s="10"/>
+      <c r="E24" s="10"/>
+      <c r="F24" s="9"/>
+      <c r="G24" s="11"/>
+      <c r="H24" s="11"/>
+      <c r="I24" s="45"/>
+      <c r="J24" s="12"/>
+      <c r="K24" s="24"/>
+    </row>
+    <row r="25" spans="2:11" ht="21.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B25" s="23"/>
+      <c r="C25" s="9"/>
+      <c r="D25" s="10"/>
+      <c r="E25" s="10"/>
+      <c r="F25" s="9"/>
+      <c r="G25" s="11"/>
+      <c r="H25" s="11"/>
+      <c r="I25" s="45"/>
+      <c r="J25" s="12"/>
+      <c r="K25" s="24"/>
+    </row>
+    <row r="26" spans="2:11" ht="21.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B26" s="23"/>
+      <c r="C26" s="9"/>
+      <c r="D26" s="10"/>
+      <c r="E26" s="10"/>
+      <c r="F26" s="9"/>
+      <c r="G26" s="11"/>
+      <c r="H26" s="11"/>
+      <c r="I26" s="45"/>
+      <c r="J26" s="12"/>
+      <c r="K26" s="24"/>
+    </row>
+    <row r="27" spans="2:11" ht="21.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B27" s="23"/>
+      <c r="C27" s="9"/>
+      <c r="D27" s="10"/>
+      <c r="E27" s="10"/>
+      <c r="F27" s="9"/>
+      <c r="G27" s="11"/>
+      <c r="H27" s="11"/>
+      <c r="I27" s="45"/>
+      <c r="J27" s="12"/>
+      <c r="K27" s="46"/>
+    </row>
+    <row r="28" spans="2:11" ht="21.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B28" s="23"/>
+      <c r="C28" s="9"/>
+      <c r="D28" s="10"/>
+      <c r="E28" s="10"/>
+      <c r="F28" s="9"/>
+      <c r="G28" s="11"/>
+      <c r="H28" s="11"/>
+      <c r="I28" s="45"/>
+      <c r="J28" s="12"/>
+      <c r="K28" s="24"/>
+    </row>
+    <row r="29" spans="2:11" ht="21.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B29" s="23"/>
+      <c r="C29" s="9"/>
+      <c r="D29" s="10"/>
+      <c r="E29" s="10"/>
+      <c r="F29" s="9"/>
+      <c r="G29" s="11"/>
+      <c r="H29" s="11"/>
+      <c r="I29" s="45"/>
+      <c r="J29" s="12"/>
+      <c r="K29" s="24"/>
+    </row>
+    <row r="30" spans="2:11" ht="21.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B30" s="23"/>
+      <c r="C30" s="9"/>
+      <c r="D30" s="10"/>
+      <c r="E30" s="10"/>
+      <c r="F30" s="9"/>
+      <c r="G30" s="11"/>
+      <c r="H30" s="11"/>
+      <c r="I30" s="45"/>
+      <c r="J30" s="12"/>
+      <c r="K30" s="24"/>
+    </row>
+    <row r="31" spans="2:11" ht="21.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B31" s="23"/>
+      <c r="C31" s="9"/>
+      <c r="D31" s="10"/>
+      <c r="E31" s="10"/>
+      <c r="F31" s="9"/>
+      <c r="G31" s="11"/>
+      <c r="H31" s="11"/>
+      <c r="I31" s="45"/>
+      <c r="J31" s="12"/>
+      <c r="K31" s="46"/>
+    </row>
+    <row r="32" spans="2:11" ht="21.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B32" s="23"/>
+      <c r="C32" s="9"/>
+      <c r="D32" s="10"/>
+      <c r="E32" s="10"/>
+      <c r="F32" s="9"/>
+      <c r="G32" s="11"/>
+      <c r="H32" s="11"/>
+      <c r="I32" s="45"/>
+      <c r="J32" s="12"/>
+      <c r="K32" s="24"/>
+    </row>
+    <row r="33" spans="2:11" ht="21.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B33" s="23"/>
+      <c r="C33" s="9"/>
+      <c r="D33" s="10"/>
+      <c r="E33" s="10"/>
+      <c r="F33" s="9"/>
+      <c r="G33" s="11"/>
+      <c r="H33" s="11"/>
+      <c r="I33" s="45"/>
+      <c r="J33" s="12"/>
+      <c r="K33" s="24"/>
+    </row>
+    <row r="34" spans="2:11" ht="21.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B34" s="23"/>
+      <c r="C34" s="9"/>
+      <c r="D34" s="10"/>
+      <c r="E34" s="10"/>
+      <c r="F34" s="9"/>
+      <c r="G34" s="11"/>
+      <c r="H34" s="11"/>
+      <c r="I34" s="45"/>
+      <c r="J34" s="12"/>
+      <c r="K34" s="24"/>
+    </row>
+    <row r="35" spans="2:11" ht="21.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B35" s="23"/>
+      <c r="C35" s="9"/>
+      <c r="D35" s="10"/>
+      <c r="E35" s="10"/>
+      <c r="F35" s="9"/>
+      <c r="G35" s="11"/>
+      <c r="H35" s="11"/>
+      <c r="I35" s="45"/>
+      <c r="J35" s="12"/>
+      <c r="K35" s="24"/>
+    </row>
+    <row r="36" spans="2:11" ht="21.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B36" s="23"/>
+      <c r="C36" s="9"/>
+      <c r="D36" s="10"/>
+      <c r="E36" s="10"/>
+      <c r="F36" s="9"/>
+      <c r="G36" s="11"/>
+      <c r="H36" s="11"/>
+      <c r="I36" s="45"/>
+      <c r="J36" s="12"/>
+      <c r="K36" s="24"/>
+    </row>
+    <row r="37" spans="2:11" ht="21.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B37" s="23"/>
+      <c r="C37" s="9"/>
+      <c r="D37" s="10"/>
+      <c r="E37" s="10"/>
+      <c r="F37" s="9"/>
+      <c r="G37" s="11"/>
+      <c r="H37" s="11"/>
+      <c r="I37" s="45"/>
+      <c r="J37" s="12"/>
+      <c r="K37" s="24"/>
+    </row>
+    <row r="38" spans="2:11" ht="21.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B38" s="23"/>
+      <c r="C38" s="9"/>
+      <c r="D38" s="10"/>
+      <c r="E38" s="10"/>
+      <c r="F38" s="9"/>
+      <c r="G38" s="11"/>
+      <c r="H38" s="11"/>
+      <c r="I38" s="45"/>
+      <c r="J38" s="12"/>
+      <c r="K38" s="24"/>
+    </row>
+    <row r="39" spans="2:11" ht="21.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B39" s="23"/>
+      <c r="C39" s="9"/>
+      <c r="D39" s="10"/>
+      <c r="E39" s="10"/>
+      <c r="F39" s="9"/>
+      <c r="G39" s="11"/>
+      <c r="H39" s="11"/>
+      <c r="I39" s="45"/>
+      <c r="J39" s="12"/>
+      <c r="K39" s="24"/>
+    </row>
+    <row r="40" spans="2:11" ht="21.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B40" s="23"/>
+      <c r="C40" s="9"/>
+      <c r="D40" s="10"/>
+      <c r="E40" s="10"/>
+      <c r="F40" s="9"/>
+      <c r="G40" s="11"/>
+      <c r="H40" s="11"/>
+      <c r="I40" s="45"/>
+      <c r="J40" s="12"/>
+      <c r="K40" s="24"/>
+    </row>
+    <row r="41" spans="2:11" ht="21.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B41" s="23"/>
+      <c r="C41" s="9"/>
+      <c r="D41" s="10"/>
+      <c r="E41" s="10"/>
+      <c r="F41" s="9"/>
+      <c r="G41" s="11"/>
+      <c r="H41" s="11"/>
+      <c r="I41" s="45"/>
+      <c r="J41" s="12"/>
+      <c r="K41" s="24"/>
+    </row>
+    <row r="42" spans="2:11" ht="21.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B42" s="23"/>
+      <c r="C42" s="9"/>
+      <c r="D42" s="10"/>
+      <c r="E42" s="10"/>
+      <c r="F42" s="9"/>
+      <c r="G42" s="11"/>
+      <c r="H42" s="11"/>
+      <c r="I42" s="11"/>
+      <c r="J42" s="12"/>
+      <c r="K42" s="24"/>
+    </row>
+    <row r="43" spans="2:11" ht="21.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B43" s="23"/>
+      <c r="C43" s="9"/>
+      <c r="D43" s="10"/>
+      <c r="E43" s="10"/>
+      <c r="F43" s="9"/>
+      <c r="G43" s="11"/>
+      <c r="H43" s="11"/>
+      <c r="I43" s="11"/>
+      <c r="J43" s="12"/>
+      <c r="K43" s="24"/>
+    </row>
+    <row r="44" spans="2:11" ht="21.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B44" s="23"/>
+      <c r="C44" s="9"/>
+      <c r="D44" s="10"/>
+      <c r="E44" s="10"/>
+      <c r="F44" s="9"/>
+      <c r="G44" s="11"/>
+      <c r="H44" s="11"/>
+      <c r="I44" s="11"/>
+      <c r="J44" s="12"/>
+      <c r="K44" s="24"/>
+    </row>
+    <row r="45" spans="2:11" ht="21.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B45" s="23"/>
+      <c r="C45" s="9"/>
+      <c r="D45" s="10"/>
+      <c r="E45" s="10"/>
+      <c r="F45" s="9"/>
+      <c r="G45" s="11"/>
+      <c r="H45" s="11"/>
+      <c r="I45" s="11"/>
+      <c r="J45" s="12"/>
+      <c r="K45" s="24"/>
+    </row>
+    <row r="46" spans="2:11" ht="21.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B46" s="23"/>
+      <c r="C46" s="9"/>
+      <c r="D46" s="10"/>
+      <c r="E46" s="10"/>
+      <c r="F46" s="9"/>
+      <c r="G46" s="11"/>
+      <c r="H46" s="11"/>
+      <c r="I46" s="11"/>
+      <c r="J46" s="12"/>
+      <c r="K46" s="24"/>
+    </row>
+    <row r="47" spans="2:11" ht="21.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B47" s="23"/>
+      <c r="C47" s="9"/>
+      <c r="D47" s="10"/>
+      <c r="E47" s="10"/>
+      <c r="F47" s="9"/>
+      <c r="G47" s="11"/>
+      <c r="H47" s="11"/>
+      <c r="I47" s="11"/>
+      <c r="J47" s="12"/>
+      <c r="K47" s="24"/>
+    </row>
+    <row r="48" spans="2:11" ht="21.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B48" s="23"/>
+      <c r="C48" s="9"/>
+      <c r="D48" s="10"/>
+      <c r="E48" s="10"/>
+      <c r="F48" s="9"/>
+      <c r="G48" s="11"/>
+      <c r="H48" s="11"/>
+      <c r="I48" s="11"/>
+      <c r="J48" s="12"/>
+      <c r="K48" s="24"/>
+    </row>
+    <row r="49" spans="2:11" ht="21.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B49" s="23"/>
+      <c r="C49" s="9"/>
+      <c r="D49" s="10"/>
+      <c r="E49" s="10"/>
+      <c r="F49" s="9"/>
+      <c r="G49" s="11"/>
+      <c r="H49" s="11"/>
+      <c r="I49" s="11"/>
+      <c r="J49" s="12"/>
+      <c r="K49" s="24"/>
+    </row>
+    <row r="50" spans="2:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B50" s="29"/>
+      <c r="C50" s="30" t="s">
+        <v>27</v>
+      </c>
+      <c r="D50" s="31"/>
+      <c r="E50" s="31"/>
+      <c r="F50" s="31"/>
+      <c r="G50" s="32"/>
+      <c r="H50" s="32"/>
+      <c r="I50" s="44"/>
+      <c r="J50" s="33">
+        <f>SUM(J11:J49)</f>
+      </c>
+      <c r="K50" s="34"/>
+    </row>
+    <row r="51" spans="2:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B51" s="25"/>
+      <c r="C51" s="9"/>
+      <c r="D51" s="9"/>
+      <c r="E51" s="9"/>
+      <c r="F51" s="9"/>
+      <c r="G51" s="14"/>
+      <c r="H51" s="15"/>
+      <c r="I51" s="15"/>
+      <c r="J51" s="16"/>
+      <c r="K51" s="26"/>
+    </row>
+    <row r="52" spans="2:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B52" s="25"/>
+      <c r="C52" s="9"/>
+      <c r="D52" s="9"/>
+      <c r="E52" s="9"/>
+      <c r="F52" s="9"/>
+      <c r="G52" s="14"/>
+      <c r="H52" s="15"/>
+      <c r="I52" s="15"/>
+      <c r="J52" s="16"/>
+      <c r="K52" s="26"/>
+    </row>
+    <row r="53" spans="2:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B53" s="25"/>
+      <c r="C53" s="9"/>
+      <c r="D53" s="9"/>
+      <c r="E53" s="9"/>
+      <c r="F53" s="9"/>
+      <c r="G53" s="14"/>
+      <c r="H53" s="15"/>
+      <c r="I53" s="15"/>
+      <c r="J53" s="16"/>
+      <c r="K53" s="26"/>
+    </row>
+    <row r="54" spans="2:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B54" s="27"/>
+      <c r="C54" s="17"/>
+      <c r="D54" s="17"/>
+      <c r="E54" s="17"/>
+      <c r="F54" s="17"/>
+      <c r="G54" s="18"/>
+      <c r="H54" s="19"/>
+      <c r="I54" s="19"/>
+      <c r="J54" s="20"/>
+      <c r="K54" s="28"/>
+    </row>
+    <row r="55" spans="2:11" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="B55" s="13"/>
+      <c r="C55" s="13"/>
+      <c r="D55" s="13"/>
+      <c r="E55" s="13"/>
+      <c r="F55" s="13"/>
+      <c r="G55" s="13"/>
+      <c r="H55" s="13"/>
+      <c r="I55" s="13"/>
+      <c r="J55" s="13"/>
+      <c r="K55" s="13"/>
     </row>
   </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="I7:J7"/>
+  <mergeCells count="9">
+    <mergeCell ref="J7:K7"/>
     <mergeCell ref="B8:B9"/>
     <mergeCell ref="C8:C9"/>
     <mergeCell ref="D8:D9"/>
     <mergeCell ref="E8:E9"/>
     <mergeCell ref="F8:F9"/>
     <mergeCell ref="G8:H8"/>
-    <mergeCell ref="J8:J9"/>
+    <mergeCell ref="K8:K9"/>
+    <mergeCell ref="I8:J8"/>
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="57" fitToHeight="0" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="48" fitToHeight="0" orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/템플릿/토건 명세표 템플릿.xlsx
+++ b/템플릿/토건 명세표 템플릿.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\내 드라이브\02.하이테크\온결(우진)\ON260902-3001(임근실 성남여수동 상속증여 토건) 정우진\__평가서\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50FE3616-FD54-4EE9-B04F-5C3CE9F2F223}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE7E2430-9046-465E-820E-7E7F3D7AEC52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" tabRatio="724" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet2" sheetId="4" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Sheet2'!$B$3:$K$54</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet2!$B$3:$K$57</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
   <extLst>
@@ -125,15 +125,6 @@
     <t>합  계</t>
   </si>
   <si>
-    <t xml:space="preserve">            (토지·건물)감정평가명세표</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>단가
-(원/㎡)</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t>다가구주택</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
@@ -143,6 +134,14 @@
   </si>
   <si>
     <t>x 36/50</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">              (토지·건물)감정평가명세표</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>단가(원/㎡)</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
@@ -162,9 +161,9 @@
     <numFmt numFmtId="181" formatCode="#,##0.0"/>
     <numFmt numFmtId="182" formatCode="#,##0.00##"/>
     <numFmt numFmtId="183" formatCode="#,##0.00_);[Red]\(#,##0.00\)"/>
-    <numFmt numFmtId="188" formatCode="&quot;₩&quot;#,##0"/>
+    <numFmt numFmtId="184" formatCode="&quot;₩&quot;#,##0"/>
   </numFmts>
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -211,14 +210,6 @@
       <charset val="129"/>
     </font>
     <font>
-      <b/>
-      <sz val="14"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="한컴 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
-    </font>
-    <font>
       <sz val="11"/>
       <name val="한컴 고딕"/>
       <family val="3"/>
@@ -252,15 +243,42 @@
       <charset val="129"/>
     </font>
     <font>
-      <b/>
-      <sz val="16"/>
+      <sz val="20"/>
       <name val="한컴 고딕"/>
       <family val="3"/>
       <charset val="129"/>
     </font>
     <font>
       <b/>
-      <sz val="40"/>
+      <sz val="20"/>
+      <name val="한컴 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="22"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="한컴 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="22"/>
+      <name val="한컴 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="24"/>
+      <name val="한컴 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="52"/>
       <name val="한컴 고딕"/>
       <family val="3"/>
       <charset val="129"/>
@@ -504,137 +522,158 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="42" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="41" fontId="9" fillId="0" borderId="0" xfId="17" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="183" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="183" fontId="7" fillId="0" borderId="0" xfId="17" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="7" fillId="0" borderId="0" xfId="17" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="183" fontId="10" fillId="0" borderId="4" xfId="17" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="10" fillId="0" borderId="4" xfId="17" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="11" fillId="0" borderId="4" xfId="20" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="11" fillId="0" borderId="16" xfId="17" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="12" fillId="0" borderId="3" xfId="17" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="12" fillId="0" borderId="3" xfId="17" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="12" fillId="0" borderId="3" xfId="17" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="17" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="183" fontId="12" fillId="3" borderId="3" xfId="17" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="183" fontId="12" fillId="3" borderId="9" xfId="17" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="13" fillId="3" borderId="9" xfId="17" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="183" fontId="12" fillId="0" borderId="3" xfId="17" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="12" fillId="0" borderId="3" xfId="17" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="13" fillId="0" borderId="3" xfId="20" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="13" fillId="0" borderId="9" xfId="17" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="41" fontId="10" fillId="0" borderId="0" xfId="17" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="183" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="183" fontId="8" fillId="0" borderId="0" xfId="17" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="8" fillId="0" borderId="0" xfId="17" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="11" fillId="0" borderId="3" xfId="17" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="15" fillId="0" borderId="3" xfId="17" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="11" fillId="0" borderId="3" xfId="17" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="15" fillId="0" borderId="3" xfId="17" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="183" fontId="11" fillId="0" borderId="3" xfId="17" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="11" fillId="0" borderId="3" xfId="17" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="12" fillId="0" borderId="3" xfId="20" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="183" fontId="11" fillId="0" borderId="4" xfId="17" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="11" fillId="0" borderId="4" xfId="17" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="12" fillId="0" borderId="4" xfId="20" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="14" fillId="0" borderId="0" xfId="17" applyFont="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="15" fillId="0" borderId="3" xfId="17" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" xfId="17" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="15" fillId="0" borderId="9" xfId="17" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="184" fontId="16" fillId="3" borderId="9" xfId="20" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="17" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="12" fillId="0" borderId="9" xfId="17" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="12" fillId="0" borderId="16" xfId="17" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="183" fontId="11" fillId="3" borderId="3" xfId="17" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="188" fontId="13" fillId="3" borderId="9" xfId="20" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="7" fillId="0" borderId="0" xfId="17" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="41" fontId="17" fillId="0" borderId="0" xfId="17" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="12" fillId="3" borderId="9" xfId="17" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="8" fillId="0" borderId="0" xfId="17" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="183" fontId="11" fillId="3" borderId="9" xfId="17" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="11" fillId="0" borderId="3" xfId="17" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="11" fillId="0" borderId="9" xfId="17" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="21">
@@ -679,13 +718,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>890623</xdr:colOff>
-      <xdr:row>50</xdr:row>
+      <xdr:row>53</xdr:row>
       <xdr:rowOff>134235</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
       <xdr:colOff>881658</xdr:colOff>
-      <xdr:row>54</xdr:row>
+      <xdr:row>57</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -774,16 +813,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>225280</xdr:colOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>17463</xdr:colOff>
       <xdr:row>2</xdr:row>
-      <xdr:rowOff>34638</xdr:rowOff>
+      <xdr:rowOff>450274</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>1085273</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>150089</xdr:rowOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>438729</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>11545</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
@@ -798,8 +837,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="225280" y="415638"/>
-          <a:ext cx="1640136" cy="1621308"/>
+          <a:off x="283008" y="842819"/>
+          <a:ext cx="2372448" cy="2389908"/>
           <a:chOff x="361950" y="806450"/>
           <a:chExt cx="1295400" cy="1217312"/>
         </a:xfrm>
@@ -894,7 +933,7 @@
           <a:p>
             <a:pPr algn="ctr" fontAlgn="base" latinLnBrk="0"/>
             <a:r>
-              <a:rPr lang="en-US" altLang="ko-KR" sz="2800" b="1" kern="0" spc="0">
+              <a:rPr lang="en-US" altLang="ko-KR" sz="3200" b="1" kern="0" spc="0">
                 <a:solidFill>
                   <a:srgbClr val="808080"/>
                 </a:solidFill>
@@ -905,7 +944,7 @@
               <a:t>chapter</a:t>
             </a:r>
             <a:r>
-              <a:rPr lang="en-US" altLang="ko-KR" sz="3200" b="1" kern="0" spc="0">
+              <a:rPr lang="en-US" altLang="ko-KR" sz="3600" b="1" kern="0" spc="0">
                 <a:solidFill>
                   <a:srgbClr val="808080"/>
                 </a:solidFill>
@@ -978,7 +1017,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:rPr lang="en-US" altLang="ko-KR" sz="6000" b="0">
+              <a:rPr lang="en-US" altLang="ko-KR" sz="7200" b="0">
                 <a:solidFill>
                   <a:schemeClr val="dk1"/>
                 </a:solidFill>
@@ -989,7 +1028,7 @@
               </a:rPr>
               <a:t>3</a:t>
             </a:r>
-            <a:endParaRPr lang="ko-KR" altLang="ko-KR" sz="4000" b="0">
+            <a:endParaRPr lang="ko-KR" altLang="ko-KR" sz="4800" b="0">
               <a:solidFill>
                 <a:schemeClr val="dk1"/>
               </a:solidFill>
@@ -1007,15 +1046,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>251653</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>76361</xdr:rowOff>
+      <xdr:colOff>690381</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>110998</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>803017</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>76361</xdr:rowOff>
+      <xdr:colOff>1241745</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>110998</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1032,14 +1071,14 @@
       </xdr:nvSpPr>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="2329835" y="1969816"/>
-          <a:ext cx="8460000" cy="0"/>
+          <a:off x="2907108" y="3031998"/>
+          <a:ext cx="12293092" cy="0"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
         </a:prstGeom>
         <a:noFill/>
-        <a:ln w="35941">
+        <a:ln w="57150">
           <a:solidFill>
             <a:srgbClr val="808080"/>
           </a:solidFill>
@@ -1380,706 +1419,728 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B3:K55"/>
+  <dimension ref="B3:K58"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="3.5" style="2" customWidth="1"/>
-    <col min="2" max="2" width="6.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15" style="2" customWidth="1"/>
-    <col min="4" max="4" width="11" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="19.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="22.5" style="2" customWidth="1"/>
-    <col min="7" max="7" width="13.9140625" style="2" customWidth="1"/>
-    <col min="8" max="8" width="13.83203125" style="2" customWidth="1"/>
-    <col min="9" max="9" width="14.83203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="24.9140625" style="2" customWidth="1"/>
-    <col min="11" max="11" width="13.33203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="6.5" style="2" customWidth="1"/>
-    <col min="13" max="16384" width="8.6640625" style="2"/>
+    <col min="1" max="1" width="3.5" style="1" customWidth="1"/>
+    <col min="2" max="2" width="10.6640625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="15" style="1" customWidth="1"/>
+    <col min="4" max="4" width="11" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="30.4140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.9140625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="15.6640625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="20.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="33.75" style="1" customWidth="1"/>
+    <col min="11" max="11" width="21.1640625" style="1" customWidth="1"/>
+    <col min="12" max="12" width="6.5" style="1" customWidth="1"/>
+    <col min="13" max="16384" width="8.6640625" style="1"/>
   </cols>
   <sheetData>
     <row r="3" spans="2:11" ht="52.5" x14ac:dyDescent="1.25">
-      <c r="C3" s="22"/>
-      <c r="D3" s="22"/>
-      <c r="E3" s="22"/>
-      <c r="F3" s="22"/>
-      <c r="G3" s="22"/>
-      <c r="H3" s="22"/>
-      <c r="I3" s="22"/>
-      <c r="J3" s="22"/>
-      <c r="K3" s="22"/>
+      <c r="C3" s="13"/>
+      <c r="D3" s="13"/>
+      <c r="E3" s="13"/>
+      <c r="F3" s="13"/>
+      <c r="G3" s="13"/>
+      <c r="H3" s="13"/>
+      <c r="I3" s="13"/>
+      <c r="J3" s="13"/>
+      <c r="K3" s="13"/>
     </row>
     <row r="4" spans="2:11" ht="47.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B4" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="G4" s="4"/>
-    </row>
-    <row r="5" spans="2:11" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B5" s="3"/>
-      <c r="G5" s="4"/>
+      <c r="G4" s="3"/>
+    </row>
+    <row r="5" spans="2:11" ht="68" x14ac:dyDescent="0.4">
+      <c r="B5" s="53" t="s">
+        <v>31</v>
+      </c>
+      <c r="G5" s="3"/>
     </row>
     <row r="6" spans="2:11" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B6" s="3"/>
-      <c r="G6" s="4"/>
-    </row>
-    <row r="7" spans="2:11" ht="15.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B7" s="5"/>
-      <c r="C7" s="6"/>
-      <c r="D7" s="5"/>
-      <c r="E7" s="6"/>
-      <c r="F7" s="6"/>
-      <c r="G7" s="7"/>
-      <c r="H7" s="8"/>
-      <c r="I7" s="8"/>
-      <c r="J7" s="35"/>
-      <c r="K7" s="35"/>
-    </row>
-    <row r="8" spans="2:11" ht="24.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B8" s="36" t="s">
+      <c r="B6" s="2"/>
+      <c r="G6" s="3"/>
+    </row>
+    <row r="7" spans="2:11" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B7" s="2"/>
+      <c r="G7" s="3"/>
+    </row>
+    <row r="8" spans="2:11" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B8" s="2"/>
+      <c r="G8" s="3"/>
+    </row>
+    <row r="9" spans="2:11" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B9" s="2"/>
+      <c r="G9" s="3"/>
+    </row>
+    <row r="10" spans="2:11" ht="15.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B10" s="4"/>
+      <c r="C10" s="5"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="5"/>
+      <c r="F10" s="5"/>
+      <c r="G10" s="6"/>
+      <c r="H10" s="7"/>
+      <c r="I10" s="7"/>
+      <c r="J10" s="44"/>
+      <c r="K10" s="44"/>
+    </row>
+    <row r="11" spans="2:11" ht="45.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B11" s="45" t="s">
         <v>0</v>
       </c>
-      <c r="C8" s="38" t="s">
+      <c r="C11" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="D8" s="38" t="s">
+      <c r="D11" s="47" t="s">
         <v>2</v>
       </c>
-      <c r="E8" s="38" t="s">
+      <c r="E11" s="47" t="s">
         <v>3</v>
       </c>
-      <c r="F8" s="38" t="s">
+      <c r="F11" s="47" t="s">
         <v>4</v>
       </c>
-      <c r="G8" s="40" t="s">
+      <c r="G11" s="49" t="s">
         <v>5</v>
       </c>
-      <c r="H8" s="41"/>
-      <c r="I8" s="40" t="s">
+      <c r="H11" s="50"/>
+      <c r="I11" s="49" t="s">
         <v>6</v>
       </c>
-      <c r="J8" s="41"/>
-      <c r="K8" s="42" t="s">
+      <c r="J11" s="50"/>
+      <c r="K11" s="51" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="2:11" ht="48" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="B9" s="37"/>
-      <c r="C9" s="39"/>
-      <c r="D9" s="39"/>
-      <c r="E9" s="39"/>
-      <c r="F9" s="39"/>
-      <c r="G9" s="1" t="s">
+    <row r="12" spans="2:11" ht="48" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
+      <c r="B12" s="46"/>
+      <c r="C12" s="48"/>
+      <c r="D12" s="48"/>
+      <c r="E12" s="48"/>
+      <c r="F12" s="48"/>
+      <c r="G12" s="34" t="s">
         <v>8</v>
       </c>
-      <c r="H9" s="1" t="s">
+      <c r="H12" s="34" t="s">
         <v>9</v>
       </c>
-      <c r="I9" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="J9" s="1" t="s">
+      <c r="I12" s="34" t="s">
+        <v>32</v>
+      </c>
+      <c r="J12" s="34" t="s">
         <v>10</v>
       </c>
-      <c r="K9" s="43"/>
-    </row>
-    <row r="11" spans="2:11" ht="21.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B11" s="23" t="inlineStr">
+      <c r="K12" s="52"/>
+    </row>
+    <row r="13" spans="2:11" ht="29.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B13" s="35"/>
+      <c r="C13" s="36"/>
+      <c r="D13" s="37"/>
+      <c r="E13" s="37"/>
+      <c r="F13" s="36"/>
+      <c r="G13" s="38"/>
+      <c r="H13" s="38"/>
+      <c r="I13" s="39"/>
+      <c r="J13" s="40"/>
+      <c r="K13" s="41"/>
+    </row>
+    <row r="14" spans="2:11" ht="29.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B14" s="35" t="inlineStr">
         <is>
           <t>{{명세_기호}}</t>
         </is>
       </c>
-      <c r="C11" s="9" t="inlineStr">
+      <c r="C14" s="36" t="inlineStr">
         <is>
           <t>{{명세_소재지}}</t>
         </is>
       </c>
-      <c r="D11" s="10" t="inlineStr">
+      <c r="D14" s="37" t="inlineStr">
         <is>
           <t>{{명세_지번}}</t>
         </is>
       </c>
-      <c r="E11" s="10" t="inlineStr">
+      <c r="E14" s="37" t="inlineStr">
         <is>
           <t>{{명세_지목용도}}</t>
         </is>
       </c>
-      <c r="F11" s="9" t="inlineStr">
+      <c r="F14" s="36" t="inlineStr">
         <is>
           <t>{{명세_지역구조}}</t>
         </is>
       </c>
-      <c r="G11" s="11" t="inlineStr">
+      <c r="G14" s="38" t="inlineStr">
         <is>
           <t>{{명세_공부면적}}</t>
         </is>
       </c>
-      <c r="H11" s="11" t="inlineStr">
+      <c r="H14" s="38" t="inlineStr">
         <is>
           <t>{{명세_사정면적}}</t>
         </is>
       </c>
-      <c r="I11" s="45" t="inlineStr">
+      <c r="I14" s="39" t="inlineStr">
         <is>
           <t>{{명세_단가}}</t>
         </is>
       </c>
-      <c r="J11" s="12">
-        <f>+I11*H11</f>
-      </c>
-      <c r="K11" s="24" t="inlineStr">
+      <c r="J14" s="40">
+        <f>+I14*H14</f>
+      </c>
+      <c r="K14" s="42" t="inlineStr">
         <is>
           <t>{{명세_비고}}</t>
         </is>
       </c>
     </row>
-    <row r="12" spans="2:11" ht="21.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B12" s="23"/>
-      <c r="C12" s="9"/>
-      <c r="D12" s="10"/>
-      <c r="E12" s="10"/>
-      <c r="F12" s="9"/>
-      <c r="G12" s="11"/>
-      <c r="H12" s="11"/>
-      <c r="I12" s="11"/>
-      <c r="J12" s="12"/>
-      <c r="K12" s="24"/>
-    </row>
-    <row r="13" spans="2:11" ht="21.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B13" s="23"/>
-      <c r="C13" s="9"/>
-      <c r="D13" s="10"/>
-      <c r="E13" s="10"/>
-      <c r="F13" s="9"/>
-      <c r="G13" s="11"/>
-      <c r="H13" s="11"/>
-      <c r="I13" s="45"/>
-      <c r="J13" s="12"/>
-      <c r="K13" s="24"/>
-    </row>
-    <row r="14" spans="2:11" ht="21.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B14" s="23"/>
-      <c r="C14" s="9"/>
-      <c r="D14" s="10"/>
-      <c r="E14" s="10"/>
-      <c r="F14" s="9"/>
-      <c r="G14" s="11"/>
-      <c r="H14" s="11"/>
-      <c r="I14" s="45"/>
-      <c r="J14" s="12"/>
-      <c r="K14" s="24"/>
-    </row>
-    <row r="15" spans="2:11" ht="21.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B15" s="23"/>
-      <c r="C15" s="9"/>
-      <c r="D15" s="10"/>
-      <c r="E15" s="10"/>
-      <c r="F15" s="9"/>
-      <c r="G15" s="11"/>
-      <c r="H15" s="11"/>
-      <c r="I15" s="45"/>
-      <c r="J15" s="12"/>
-      <c r="K15" s="46"/>
-    </row>
-    <row r="16" spans="2:11" ht="21.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B16" s="23"/>
-      <c r="C16" s="9"/>
-      <c r="D16" s="10"/>
-      <c r="E16" s="10"/>
-      <c r="F16" s="9"/>
-      <c r="G16" s="11"/>
-      <c r="H16" s="11"/>
-      <c r="I16" s="45"/>
-      <c r="J16" s="12"/>
-      <c r="K16" s="24"/>
-    </row>
-    <row r="17" spans="2:11" ht="21.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B17" s="23"/>
-      <c r="C17" s="9"/>
-      <c r="D17" s="10"/>
-      <c r="E17" s="10"/>
-      <c r="F17" s="9"/>
-      <c r="G17" s="11"/>
-      <c r="H17" s="11"/>
-      <c r="I17" s="45"/>
-      <c r="J17" s="12"/>
-      <c r="K17" s="24"/>
-    </row>
-    <row r="18" spans="2:11" ht="21.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B18" s="23"/>
-      <c r="C18" s="9"/>
-      <c r="D18" s="10"/>
-      <c r="E18" s="10"/>
-      <c r="F18" s="9"/>
-      <c r="G18" s="11"/>
-      <c r="H18" s="11"/>
-      <c r="I18" s="45"/>
-      <c r="J18" s="12"/>
-      <c r="K18" s="24"/>
-    </row>
-    <row r="19" spans="2:11" ht="21.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B19" s="23"/>
-      <c r="C19" s="9"/>
-      <c r="D19" s="10"/>
-      <c r="E19" s="10"/>
-      <c r="F19" s="9"/>
-      <c r="G19" s="11"/>
-      <c r="H19" s="11"/>
-      <c r="I19" s="45"/>
-      <c r="J19" s="12"/>
-      <c r="K19" s="46"/>
-    </row>
-    <row r="20" spans="2:11" ht="21.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B20" s="23"/>
-      <c r="C20" s="9"/>
-      <c r="D20" s="10"/>
-      <c r="E20" s="10"/>
-      <c r="F20" s="9"/>
-      <c r="G20" s="11"/>
-      <c r="H20" s="11"/>
-      <c r="I20" s="45"/>
-      <c r="J20" s="12"/>
-      <c r="K20" s="24"/>
-    </row>
-    <row r="21" spans="2:11" ht="21.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B21" s="23"/>
-      <c r="C21" s="9"/>
-      <c r="D21" s="10"/>
-      <c r="E21" s="10"/>
-      <c r="F21" s="9"/>
-      <c r="G21" s="11"/>
-      <c r="H21" s="11"/>
-      <c r="I21" s="45"/>
-      <c r="J21" s="12"/>
-      <c r="K21" s="24"/>
-    </row>
-    <row r="22" spans="2:11" ht="21.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B22" s="23"/>
-      <c r="C22" s="9"/>
-      <c r="D22" s="10"/>
-      <c r="E22" s="10"/>
-      <c r="F22" s="9"/>
-      <c r="G22" s="11"/>
-      <c r="H22" s="11"/>
-      <c r="I22" s="45"/>
-      <c r="J22" s="12"/>
-      <c r="K22" s="24"/>
-    </row>
-    <row r="23" spans="2:11" ht="21.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B23" s="23"/>
-      <c r="C23" s="9"/>
-      <c r="D23" s="10"/>
-      <c r="E23" s="10"/>
-      <c r="F23" s="9"/>
-      <c r="G23" s="11"/>
-      <c r="H23" s="11"/>
-      <c r="I23" s="45"/>
-      <c r="J23" s="12"/>
-      <c r="K23" s="46"/>
-    </row>
-    <row r="24" spans="2:11" ht="21.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B24" s="23"/>
-      <c r="C24" s="9"/>
-      <c r="D24" s="10"/>
-      <c r="E24" s="10"/>
-      <c r="F24" s="9"/>
-      <c r="G24" s="11"/>
-      <c r="H24" s="11"/>
-      <c r="I24" s="45"/>
-      <c r="J24" s="12"/>
-      <c r="K24" s="24"/>
-    </row>
-    <row r="25" spans="2:11" ht="21.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B25" s="23"/>
-      <c r="C25" s="9"/>
-      <c r="D25" s="10"/>
-      <c r="E25" s="10"/>
-      <c r="F25" s="9"/>
-      <c r="G25" s="11"/>
-      <c r="H25" s="11"/>
-      <c r="I25" s="45"/>
-      <c r="J25" s="12"/>
-      <c r="K25" s="24"/>
-    </row>
-    <row r="26" spans="2:11" ht="21.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B26" s="23"/>
-      <c r="C26" s="9"/>
-      <c r="D26" s="10"/>
-      <c r="E26" s="10"/>
-      <c r="F26" s="9"/>
-      <c r="G26" s="11"/>
-      <c r="H26" s="11"/>
-      <c r="I26" s="45"/>
-      <c r="J26" s="12"/>
-      <c r="K26" s="24"/>
-    </row>
-    <row r="27" spans="2:11" ht="21.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B27" s="23"/>
-      <c r="C27" s="9"/>
-      <c r="D27" s="10"/>
-      <c r="E27" s="10"/>
-      <c r="F27" s="9"/>
-      <c r="G27" s="11"/>
-      <c r="H27" s="11"/>
-      <c r="I27" s="45"/>
-      <c r="J27" s="12"/>
-      <c r="K27" s="46"/>
-    </row>
-    <row r="28" spans="2:11" ht="21.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B28" s="23"/>
-      <c r="C28" s="9"/>
-      <c r="D28" s="10"/>
-      <c r="E28" s="10"/>
-      <c r="F28" s="9"/>
-      <c r="G28" s="11"/>
-      <c r="H28" s="11"/>
-      <c r="I28" s="45"/>
-      <c r="J28" s="12"/>
-      <c r="K28" s="24"/>
-    </row>
-    <row r="29" spans="2:11" ht="21.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B29" s="23"/>
-      <c r="C29" s="9"/>
-      <c r="D29" s="10"/>
-      <c r="E29" s="10"/>
-      <c r="F29" s="9"/>
-      <c r="G29" s="11"/>
-      <c r="H29" s="11"/>
-      <c r="I29" s="45"/>
-      <c r="J29" s="12"/>
-      <c r="K29" s="24"/>
-    </row>
-    <row r="30" spans="2:11" ht="21.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B30" s="23"/>
-      <c r="C30" s="9"/>
-      <c r="D30" s="10"/>
-      <c r="E30" s="10"/>
-      <c r="F30" s="9"/>
-      <c r="G30" s="11"/>
-      <c r="H30" s="11"/>
-      <c r="I30" s="45"/>
-      <c r="J30" s="12"/>
-      <c r="K30" s="24"/>
-    </row>
-    <row r="31" spans="2:11" ht="21.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B31" s="23"/>
-      <c r="C31" s="9"/>
-      <c r="D31" s="10"/>
-      <c r="E31" s="10"/>
-      <c r="F31" s="9"/>
-      <c r="G31" s="11"/>
-      <c r="H31" s="11"/>
-      <c r="I31" s="45"/>
-      <c r="J31" s="12"/>
-      <c r="K31" s="46"/>
-    </row>
-    <row r="32" spans="2:11" ht="21.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B32" s="23"/>
-      <c r="C32" s="9"/>
-      <c r="D32" s="10"/>
-      <c r="E32" s="10"/>
-      <c r="F32" s="9"/>
-      <c r="G32" s="11"/>
-      <c r="H32" s="11"/>
-      <c r="I32" s="45"/>
-      <c r="J32" s="12"/>
-      <c r="K32" s="24"/>
-    </row>
-    <row r="33" spans="2:11" ht="21.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B33" s="23"/>
-      <c r="C33" s="9"/>
-      <c r="D33" s="10"/>
-      <c r="E33" s="10"/>
-      <c r="F33" s="9"/>
-      <c r="G33" s="11"/>
-      <c r="H33" s="11"/>
-      <c r="I33" s="45"/>
-      <c r="J33" s="12"/>
-      <c r="K33" s="24"/>
-    </row>
-    <row r="34" spans="2:11" ht="21.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B34" s="23"/>
-      <c r="C34" s="9"/>
-      <c r="D34" s="10"/>
-      <c r="E34" s="10"/>
-      <c r="F34" s="9"/>
-      <c r="G34" s="11"/>
-      <c r="H34" s="11"/>
-      <c r="I34" s="45"/>
-      <c r="J34" s="12"/>
-      <c r="K34" s="24"/>
-    </row>
-    <row r="35" spans="2:11" ht="21.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B35" s="23"/>
-      <c r="C35" s="9"/>
-      <c r="D35" s="10"/>
-      <c r="E35" s="10"/>
-      <c r="F35" s="9"/>
-      <c r="G35" s="11"/>
-      <c r="H35" s="11"/>
-      <c r="I35" s="45"/>
-      <c r="J35" s="12"/>
-      <c r="K35" s="24"/>
-    </row>
-    <row r="36" spans="2:11" ht="21.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B36" s="23"/>
-      <c r="C36" s="9"/>
-      <c r="D36" s="10"/>
-      <c r="E36" s="10"/>
-      <c r="F36" s="9"/>
-      <c r="G36" s="11"/>
-      <c r="H36" s="11"/>
-      <c r="I36" s="45"/>
-      <c r="J36" s="12"/>
-      <c r="K36" s="24"/>
-    </row>
-    <row r="37" spans="2:11" ht="21.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B37" s="23"/>
-      <c r="C37" s="9"/>
-      <c r="D37" s="10"/>
-      <c r="E37" s="10"/>
-      <c r="F37" s="9"/>
-      <c r="G37" s="11"/>
-      <c r="H37" s="11"/>
-      <c r="I37" s="45"/>
-      <c r="J37" s="12"/>
-      <c r="K37" s="24"/>
-    </row>
-    <row r="38" spans="2:11" ht="21.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B38" s="23"/>
-      <c r="C38" s="9"/>
-      <c r="D38" s="10"/>
-      <c r="E38" s="10"/>
-      <c r="F38" s="9"/>
-      <c r="G38" s="11"/>
-      <c r="H38" s="11"/>
-      <c r="I38" s="45"/>
-      <c r="J38" s="12"/>
-      <c r="K38" s="24"/>
-    </row>
-    <row r="39" spans="2:11" ht="21.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B39" s="23"/>
-      <c r="C39" s="9"/>
-      <c r="D39" s="10"/>
-      <c r="E39" s="10"/>
-      <c r="F39" s="9"/>
-      <c r="G39" s="11"/>
-      <c r="H39" s="11"/>
-      <c r="I39" s="45"/>
-      <c r="J39" s="12"/>
-      <c r="K39" s="24"/>
-    </row>
-    <row r="40" spans="2:11" ht="21.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B40" s="23"/>
-      <c r="C40" s="9"/>
-      <c r="D40" s="10"/>
-      <c r="E40" s="10"/>
-      <c r="F40" s="9"/>
-      <c r="G40" s="11"/>
-      <c r="H40" s="11"/>
-      <c r="I40" s="45"/>
-      <c r="J40" s="12"/>
-      <c r="K40" s="24"/>
-    </row>
-    <row r="41" spans="2:11" ht="21.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B41" s="23"/>
-      <c r="C41" s="9"/>
-      <c r="D41" s="10"/>
-      <c r="E41" s="10"/>
-      <c r="F41" s="9"/>
-      <c r="G41" s="11"/>
-      <c r="H41" s="11"/>
-      <c r="I41" s="45"/>
-      <c r="J41" s="12"/>
-      <c r="K41" s="24"/>
-    </row>
-    <row r="42" spans="2:11" ht="21.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B42" s="23"/>
-      <c r="C42" s="9"/>
-      <c r="D42" s="10"/>
-      <c r="E42" s="10"/>
-      <c r="F42" s="9"/>
-      <c r="G42" s="11"/>
-      <c r="H42" s="11"/>
-      <c r="I42" s="11"/>
-      <c r="J42" s="12"/>
-      <c r="K42" s="24"/>
-    </row>
-    <row r="43" spans="2:11" ht="21.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B43" s="23"/>
-      <c r="C43" s="9"/>
-      <c r="D43" s="10"/>
-      <c r="E43" s="10"/>
-      <c r="F43" s="9"/>
-      <c r="G43" s="11"/>
-      <c r="H43" s="11"/>
-      <c r="I43" s="11"/>
-      <c r="J43" s="12"/>
-      <c r="K43" s="24"/>
-    </row>
-    <row r="44" spans="2:11" ht="21.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B44" s="23"/>
-      <c r="C44" s="9"/>
-      <c r="D44" s="10"/>
-      <c r="E44" s="10"/>
-      <c r="F44" s="9"/>
-      <c r="G44" s="11"/>
-      <c r="H44" s="11"/>
-      <c r="I44" s="11"/>
-      <c r="J44" s="12"/>
-      <c r="K44" s="24"/>
-    </row>
-    <row r="45" spans="2:11" ht="21.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B45" s="23"/>
-      <c r="C45" s="9"/>
-      <c r="D45" s="10"/>
-      <c r="E45" s="10"/>
-      <c r="F45" s="9"/>
-      <c r="G45" s="11"/>
-      <c r="H45" s="11"/>
-      <c r="I45" s="11"/>
-      <c r="J45" s="12"/>
-      <c r="K45" s="24"/>
-    </row>
-    <row r="46" spans="2:11" ht="21.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B46" s="23"/>
-      <c r="C46" s="9"/>
-      <c r="D46" s="10"/>
-      <c r="E46" s="10"/>
-      <c r="F46" s="9"/>
-      <c r="G46" s="11"/>
-      <c r="H46" s="11"/>
-      <c r="I46" s="11"/>
-      <c r="J46" s="12"/>
-      <c r="K46" s="24"/>
-    </row>
-    <row r="47" spans="2:11" ht="21.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B47" s="23"/>
-      <c r="C47" s="9"/>
-      <c r="D47" s="10"/>
-      <c r="E47" s="10"/>
-      <c r="F47" s="9"/>
-      <c r="G47" s="11"/>
-      <c r="H47" s="11"/>
-      <c r="I47" s="11"/>
-      <c r="J47" s="12"/>
-      <c r="K47" s="24"/>
-    </row>
-    <row r="48" spans="2:11" ht="21.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B48" s="23"/>
-      <c r="C48" s="9"/>
-      <c r="D48" s="10"/>
-      <c r="E48" s="10"/>
-      <c r="F48" s="9"/>
-      <c r="G48" s="11"/>
-      <c r="H48" s="11"/>
-      <c r="I48" s="11"/>
-      <c r="J48" s="12"/>
-      <c r="K48" s="24"/>
-    </row>
-    <row r="49" spans="2:11" ht="21.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B49" s="23"/>
-      <c r="C49" s="9"/>
-      <c r="D49" s="10"/>
-      <c r="E49" s="10"/>
-      <c r="F49" s="9"/>
-      <c r="G49" s="11"/>
-      <c r="H49" s="11"/>
-      <c r="I49" s="11"/>
-      <c r="J49" s="12"/>
-      <c r="K49" s="24"/>
-    </row>
-    <row r="50" spans="2:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B50" s="29"/>
-      <c r="C50" s="30" t="s">
+    <row r="15" spans="2:11" ht="29.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B15" s="35"/>
+      <c r="C15" s="36"/>
+      <c r="D15" s="37"/>
+      <c r="E15" s="37"/>
+      <c r="F15" s="36"/>
+      <c r="G15" s="38"/>
+      <c r="H15" s="38"/>
+      <c r="I15" s="38"/>
+      <c r="J15" s="40"/>
+      <c r="K15" s="41"/>
+    </row>
+    <row r="16" spans="2:11" ht="29.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B16" s="35"/>
+      <c r="C16" s="36"/>
+      <c r="D16" s="37"/>
+      <c r="E16" s="37"/>
+      <c r="F16" s="36"/>
+      <c r="G16" s="38"/>
+      <c r="H16" s="38"/>
+      <c r="I16" s="39"/>
+      <c r="J16" s="40"/>
+      <c r="K16" s="41"/>
+    </row>
+    <row r="17" spans="2:11" ht="29.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B17" s="35"/>
+      <c r="C17" s="36"/>
+      <c r="D17" s="37"/>
+      <c r="E17" s="37"/>
+      <c r="F17" s="36"/>
+      <c r="G17" s="38"/>
+      <c r="H17" s="38"/>
+      <c r="I17" s="39"/>
+      <c r="J17" s="40"/>
+      <c r="K17" s="41"/>
+    </row>
+    <row r="18" spans="2:11" ht="29.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B18" s="35"/>
+      <c r="C18" s="36"/>
+      <c r="D18" s="37"/>
+      <c r="E18" s="37"/>
+      <c r="F18" s="36"/>
+      <c r="G18" s="38"/>
+      <c r="H18" s="38"/>
+      <c r="I18" s="39"/>
+      <c r="J18" s="40"/>
+      <c r="K18" s="42"/>
+    </row>
+    <row r="19" spans="2:11" ht="29.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B19" s="35"/>
+      <c r="C19" s="36"/>
+      <c r="D19" s="37"/>
+      <c r="E19" s="37"/>
+      <c r="F19" s="36"/>
+      <c r="G19" s="38"/>
+      <c r="H19" s="38"/>
+      <c r="I19" s="39"/>
+      <c r="J19" s="40"/>
+      <c r="K19" s="41"/>
+    </row>
+    <row r="20" spans="2:11" ht="29.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B20" s="35"/>
+      <c r="C20" s="36"/>
+      <c r="D20" s="37"/>
+      <c r="E20" s="37"/>
+      <c r="F20" s="36"/>
+      <c r="G20" s="38"/>
+      <c r="H20" s="38"/>
+      <c r="I20" s="39"/>
+      <c r="J20" s="40"/>
+      <c r="K20" s="41"/>
+    </row>
+    <row r="21" spans="2:11" ht="29.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B21" s="35"/>
+      <c r="C21" s="36"/>
+      <c r="D21" s="37"/>
+      <c r="E21" s="37"/>
+      <c r="F21" s="36"/>
+      <c r="G21" s="38"/>
+      <c r="H21" s="38"/>
+      <c r="I21" s="39"/>
+      <c r="J21" s="40"/>
+      <c r="K21" s="41"/>
+    </row>
+    <row r="22" spans="2:11" ht="29.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B22" s="35"/>
+      <c r="C22" s="36"/>
+      <c r="D22" s="37"/>
+      <c r="E22" s="37"/>
+      <c r="F22" s="36"/>
+      <c r="G22" s="38"/>
+      <c r="H22" s="38"/>
+      <c r="I22" s="39"/>
+      <c r="J22" s="40"/>
+      <c r="K22" s="42"/>
+    </row>
+    <row r="23" spans="2:11" ht="29.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B23" s="35"/>
+      <c r="C23" s="36"/>
+      <c r="D23" s="37"/>
+      <c r="E23" s="37"/>
+      <c r="F23" s="36"/>
+      <c r="G23" s="38"/>
+      <c r="H23" s="38"/>
+      <c r="I23" s="39"/>
+      <c r="J23" s="40"/>
+      <c r="K23" s="41"/>
+    </row>
+    <row r="24" spans="2:11" ht="29.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B24" s="35"/>
+      <c r="C24" s="36"/>
+      <c r="D24" s="37"/>
+      <c r="E24" s="37"/>
+      <c r="F24" s="36"/>
+      <c r="G24" s="38"/>
+      <c r="H24" s="38"/>
+      <c r="I24" s="39"/>
+      <c r="J24" s="40"/>
+      <c r="K24" s="41"/>
+    </row>
+    <row r="25" spans="2:11" ht="29.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B25" s="35"/>
+      <c r="C25" s="36"/>
+      <c r="D25" s="37"/>
+      <c r="E25" s="37"/>
+      <c r="F25" s="36"/>
+      <c r="G25" s="38"/>
+      <c r="H25" s="38"/>
+      <c r="I25" s="39"/>
+      <c r="J25" s="40"/>
+      <c r="K25" s="41"/>
+    </row>
+    <row r="26" spans="2:11" ht="29.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B26" s="35"/>
+      <c r="C26" s="36"/>
+      <c r="D26" s="37"/>
+      <c r="E26" s="37"/>
+      <c r="F26" s="36"/>
+      <c r="G26" s="38"/>
+      <c r="H26" s="38"/>
+      <c r="I26" s="39"/>
+      <c r="J26" s="40"/>
+      <c r="K26" s="42"/>
+    </row>
+    <row r="27" spans="2:11" ht="29.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B27" s="35"/>
+      <c r="C27" s="36"/>
+      <c r="D27" s="37"/>
+      <c r="E27" s="37"/>
+      <c r="F27" s="36"/>
+      <c r="G27" s="38"/>
+      <c r="H27" s="38"/>
+      <c r="I27" s="39"/>
+      <c r="J27" s="40"/>
+      <c r="K27" s="41"/>
+    </row>
+    <row r="28" spans="2:11" ht="29.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B28" s="35"/>
+      <c r="C28" s="36"/>
+      <c r="D28" s="37"/>
+      <c r="E28" s="37"/>
+      <c r="F28" s="36"/>
+      <c r="G28" s="38"/>
+      <c r="H28" s="38"/>
+      <c r="I28" s="39"/>
+      <c r="J28" s="40"/>
+      <c r="K28" s="41"/>
+    </row>
+    <row r="29" spans="2:11" ht="29.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B29" s="35"/>
+      <c r="C29" s="36"/>
+      <c r="D29" s="37"/>
+      <c r="E29" s="37"/>
+      <c r="F29" s="36"/>
+      <c r="G29" s="38"/>
+      <c r="H29" s="38"/>
+      <c r="I29" s="39"/>
+      <c r="J29" s="40"/>
+      <c r="K29" s="41"/>
+    </row>
+    <row r="30" spans="2:11" ht="29.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B30" s="35"/>
+      <c r="C30" s="36"/>
+      <c r="D30" s="37"/>
+      <c r="E30" s="37"/>
+      <c r="F30" s="36"/>
+      <c r="G30" s="38"/>
+      <c r="H30" s="38"/>
+      <c r="I30" s="39"/>
+      <c r="J30" s="40"/>
+      <c r="K30" s="42"/>
+    </row>
+    <row r="31" spans="2:11" ht="29.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B31" s="35"/>
+      <c r="C31" s="36"/>
+      <c r="D31" s="37"/>
+      <c r="E31" s="37"/>
+      <c r="F31" s="36"/>
+      <c r="G31" s="38"/>
+      <c r="H31" s="38"/>
+      <c r="I31" s="39"/>
+      <c r="J31" s="40"/>
+      <c r="K31" s="41"/>
+    </row>
+    <row r="32" spans="2:11" ht="29.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B32" s="35"/>
+      <c r="C32" s="36"/>
+      <c r="D32" s="37"/>
+      <c r="E32" s="37"/>
+      <c r="F32" s="36"/>
+      <c r="G32" s="38"/>
+      <c r="H32" s="38"/>
+      <c r="I32" s="39"/>
+      <c r="J32" s="40"/>
+      <c r="K32" s="41"/>
+    </row>
+    <row r="33" spans="2:11" ht="29.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B33" s="35"/>
+      <c r="C33" s="36"/>
+      <c r="D33" s="37"/>
+      <c r="E33" s="37"/>
+      <c r="F33" s="36"/>
+      <c r="G33" s="38"/>
+      <c r="H33" s="38"/>
+      <c r="I33" s="39"/>
+      <c r="J33" s="40"/>
+      <c r="K33" s="41"/>
+    </row>
+    <row r="34" spans="2:11" ht="29.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B34" s="35"/>
+      <c r="C34" s="36"/>
+      <c r="D34" s="37"/>
+      <c r="E34" s="37"/>
+      <c r="F34" s="36"/>
+      <c r="G34" s="38"/>
+      <c r="H34" s="38"/>
+      <c r="I34" s="39"/>
+      <c r="J34" s="40"/>
+      <c r="K34" s="42"/>
+    </row>
+    <row r="35" spans="2:11" ht="29.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B35" s="35"/>
+      <c r="C35" s="36"/>
+      <c r="D35" s="37"/>
+      <c r="E35" s="37"/>
+      <c r="F35" s="36"/>
+      <c r="G35" s="38"/>
+      <c r="H35" s="38"/>
+      <c r="I35" s="39"/>
+      <c r="J35" s="40"/>
+      <c r="K35" s="41"/>
+    </row>
+    <row r="36" spans="2:11" ht="29.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B36" s="35"/>
+      <c r="C36" s="36"/>
+      <c r="D36" s="37"/>
+      <c r="E36" s="37"/>
+      <c r="F36" s="36"/>
+      <c r="G36" s="38"/>
+      <c r="H36" s="38"/>
+      <c r="I36" s="39"/>
+      <c r="J36" s="40"/>
+      <c r="K36" s="41"/>
+    </row>
+    <row r="37" spans="2:11" ht="29.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B37" s="16"/>
+      <c r="C37" s="17"/>
+      <c r="D37" s="18"/>
+      <c r="E37" s="18"/>
+      <c r="F37" s="17"/>
+      <c r="G37" s="19"/>
+      <c r="H37" s="19"/>
+      <c r="I37" s="20"/>
+      <c r="J37" s="21"/>
+      <c r="K37" s="22"/>
+    </row>
+    <row r="38" spans="2:11" ht="29.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B38" s="16"/>
+      <c r="C38" s="17"/>
+      <c r="D38" s="18"/>
+      <c r="E38" s="18"/>
+      <c r="F38" s="17"/>
+      <c r="G38" s="19"/>
+      <c r="H38" s="19"/>
+      <c r="I38" s="20"/>
+      <c r="J38" s="21"/>
+      <c r="K38" s="22"/>
+    </row>
+    <row r="39" spans="2:11" ht="29.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B39" s="16"/>
+      <c r="C39" s="17"/>
+      <c r="D39" s="18"/>
+      <c r="E39" s="18"/>
+      <c r="F39" s="17"/>
+      <c r="G39" s="19"/>
+      <c r="H39" s="19"/>
+      <c r="I39" s="20"/>
+      <c r="J39" s="21"/>
+      <c r="K39" s="22"/>
+    </row>
+    <row r="40" spans="2:11" ht="29.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B40" s="16"/>
+      <c r="C40" s="17"/>
+      <c r="D40" s="18"/>
+      <c r="E40" s="18"/>
+      <c r="F40" s="17"/>
+      <c r="G40" s="19"/>
+      <c r="H40" s="19"/>
+      <c r="I40" s="20"/>
+      <c r="J40" s="21"/>
+      <c r="K40" s="22"/>
+    </row>
+    <row r="41" spans="2:11" ht="29.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B41" s="16"/>
+      <c r="C41" s="17"/>
+      <c r="D41" s="18"/>
+      <c r="E41" s="18"/>
+      <c r="F41" s="17"/>
+      <c r="G41" s="19"/>
+      <c r="H41" s="19"/>
+      <c r="I41" s="20"/>
+      <c r="J41" s="21"/>
+      <c r="K41" s="22"/>
+    </row>
+    <row r="42" spans="2:11" ht="29.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B42" s="16"/>
+      <c r="C42" s="17"/>
+      <c r="D42" s="18"/>
+      <c r="E42" s="18"/>
+      <c r="F42" s="17"/>
+      <c r="G42" s="19"/>
+      <c r="H42" s="19"/>
+      <c r="I42" s="20"/>
+      <c r="J42" s="21"/>
+      <c r="K42" s="22"/>
+    </row>
+    <row r="43" spans="2:11" ht="29.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B43" s="16"/>
+      <c r="C43" s="17"/>
+      <c r="D43" s="18"/>
+      <c r="E43" s="18"/>
+      <c r="F43" s="17"/>
+      <c r="G43" s="19"/>
+      <c r="H43" s="19"/>
+      <c r="I43" s="20"/>
+      <c r="J43" s="21"/>
+      <c r="K43" s="22"/>
+    </row>
+    <row r="44" spans="2:11" ht="29.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B44" s="16"/>
+      <c r="C44" s="17"/>
+      <c r="D44" s="18"/>
+      <c r="E44" s="18"/>
+      <c r="F44" s="17"/>
+      <c r="G44" s="19"/>
+      <c r="H44" s="19"/>
+      <c r="I44" s="20"/>
+      <c r="J44" s="21"/>
+      <c r="K44" s="22"/>
+    </row>
+    <row r="45" spans="2:11" ht="29.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B45" s="16"/>
+      <c r="C45" s="17"/>
+      <c r="D45" s="18"/>
+      <c r="E45" s="18"/>
+      <c r="F45" s="17"/>
+      <c r="G45" s="19"/>
+      <c r="H45" s="19"/>
+      <c r="I45" s="19"/>
+      <c r="J45" s="21"/>
+      <c r="K45" s="22"/>
+    </row>
+    <row r="46" spans="2:11" ht="29.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B46" s="16"/>
+      <c r="C46" s="17"/>
+      <c r="D46" s="18"/>
+      <c r="E46" s="18"/>
+      <c r="F46" s="17"/>
+      <c r="G46" s="19"/>
+      <c r="H46" s="19"/>
+      <c r="I46" s="19"/>
+      <c r="J46" s="21"/>
+      <c r="K46" s="22"/>
+    </row>
+    <row r="47" spans="2:11" ht="29.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B47" s="16"/>
+      <c r="C47" s="17"/>
+      <c r="D47" s="18"/>
+      <c r="E47" s="18"/>
+      <c r="F47" s="17"/>
+      <c r="G47" s="19"/>
+      <c r="H47" s="19"/>
+      <c r="I47" s="19"/>
+      <c r="J47" s="21"/>
+      <c r="K47" s="22"/>
+    </row>
+    <row r="48" spans="2:11" ht="29.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B48" s="16"/>
+      <c r="C48" s="17"/>
+      <c r="D48" s="18"/>
+      <c r="E48" s="18"/>
+      <c r="F48" s="17"/>
+      <c r="G48" s="19"/>
+      <c r="H48" s="19"/>
+      <c r="I48" s="19"/>
+      <c r="J48" s="21"/>
+      <c r="K48" s="22"/>
+    </row>
+    <row r="49" spans="2:11" ht="29.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B49" s="16"/>
+      <c r="C49" s="17"/>
+      <c r="D49" s="18"/>
+      <c r="E49" s="18"/>
+      <c r="F49" s="17"/>
+      <c r="G49" s="19"/>
+      <c r="H49" s="19"/>
+      <c r="I49" s="19"/>
+      <c r="J49" s="21"/>
+      <c r="K49" s="22"/>
+    </row>
+    <row r="50" spans="2:11" ht="29.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B50" s="16"/>
+      <c r="C50" s="17"/>
+      <c r="D50" s="18"/>
+      <c r="E50" s="18"/>
+      <c r="F50" s="17"/>
+      <c r="G50" s="19"/>
+      <c r="H50" s="19"/>
+      <c r="I50" s="19"/>
+      <c r="J50" s="21"/>
+      <c r="K50" s="22"/>
+    </row>
+    <row r="51" spans="2:11" ht="29.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B51" s="16"/>
+      <c r="C51" s="17"/>
+      <c r="D51" s="18"/>
+      <c r="E51" s="18"/>
+      <c r="F51" s="17"/>
+      <c r="G51" s="19"/>
+      <c r="H51" s="19"/>
+      <c r="I51" s="19"/>
+      <c r="J51" s="21"/>
+      <c r="K51" s="22"/>
+    </row>
+    <row r="52" spans="2:11" ht="29.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B52" s="16"/>
+      <c r="C52" s="17"/>
+      <c r="D52" s="18"/>
+      <c r="E52" s="18"/>
+      <c r="F52" s="17"/>
+      <c r="G52" s="19"/>
+      <c r="H52" s="19"/>
+      <c r="I52" s="19"/>
+      <c r="J52" s="21"/>
+      <c r="K52" s="22"/>
+    </row>
+    <row r="53" spans="2:11" ht="29.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B53" s="23"/>
+      <c r="C53" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="D50" s="31"/>
-      <c r="E50" s="31"/>
-      <c r="F50" s="31"/>
-      <c r="G50" s="32"/>
-      <c r="H50" s="32"/>
-      <c r="I50" s="44"/>
-      <c r="J50" s="33">
-        <f>SUM(J11:J49)</f>
-      </c>
-      <c r="K50" s="34"/>
-    </row>
-    <row r="51" spans="2:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B51" s="25"/>
-      <c r="C51" s="9"/>
-      <c r="D51" s="9"/>
-      <c r="E51" s="9"/>
-      <c r="F51" s="9"/>
-      <c r="G51" s="14"/>
-      <c r="H51" s="15"/>
-      <c r="I51" s="15"/>
-      <c r="J51" s="16"/>
-      <c r="K51" s="26"/>
-    </row>
-    <row r="52" spans="2:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B52" s="25"/>
-      <c r="C52" s="9"/>
-      <c r="D52" s="9"/>
-      <c r="E52" s="9"/>
-      <c r="F52" s="9"/>
-      <c r="G52" s="14"/>
-      <c r="H52" s="15"/>
-      <c r="I52" s="15"/>
-      <c r="J52" s="16"/>
-      <c r="K52" s="26"/>
-    </row>
-    <row r="53" spans="2:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B53" s="25"/>
-      <c r="C53" s="9"/>
-      <c r="D53" s="9"/>
-      <c r="E53" s="9"/>
-      <c r="F53" s="9"/>
-      <c r="G53" s="14"/>
-      <c r="H53" s="15"/>
-      <c r="I53" s="15"/>
-      <c r="J53" s="16"/>
-      <c r="K53" s="26"/>
-    </row>
-    <row r="54" spans="2:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B54" s="27"/>
+      <c r="D53" s="25"/>
+      <c r="E53" s="25"/>
+      <c r="F53" s="25"/>
+      <c r="G53" s="26"/>
+      <c r="H53" s="26"/>
+      <c r="I53" s="27"/>
+      <c r="J53" s="43">
+        <f>SUM(J14:J52)</f>
+      </c>
+      <c r="K53" s="28"/>
+    </row>
+    <row r="54" spans="2:11" ht="29.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B54" s="29"/>
       <c r="C54" s="17"/>
       <c r="D54" s="17"/>
       <c r="E54" s="17"/>
       <c r="F54" s="17"/>
-      <c r="G54" s="18"/>
-      <c r="H54" s="19"/>
-      <c r="I54" s="19"/>
-      <c r="J54" s="20"/>
-      <c r="K54" s="28"/>
-    </row>
-    <row r="55" spans="2:11" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="B55" s="13"/>
-      <c r="C55" s="13"/>
-      <c r="D55" s="13"/>
-      <c r="E55" s="13"/>
-      <c r="F55" s="13"/>
-      <c r="G55" s="13"/>
-      <c r="H55" s="13"/>
-      <c r="I55" s="13"/>
-      <c r="J55" s="13"/>
-      <c r="K55" s="13"/>
+      <c r="G54" s="30"/>
+      <c r="H54" s="31"/>
+      <c r="I54" s="31"/>
+      <c r="J54" s="32"/>
+      <c r="K54" s="33"/>
+    </row>
+    <row r="55" spans="2:11" ht="29.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B55" s="29"/>
+      <c r="C55" s="17"/>
+      <c r="D55" s="17"/>
+      <c r="E55" s="17"/>
+      <c r="F55" s="17"/>
+      <c r="G55" s="30"/>
+      <c r="H55" s="31"/>
+      <c r="I55" s="31"/>
+      <c r="J55" s="32"/>
+      <c r="K55" s="33"/>
+    </row>
+    <row r="56" spans="2:11" ht="29.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B56" s="29"/>
+      <c r="C56" s="17"/>
+      <c r="D56" s="17"/>
+      <c r="E56" s="17"/>
+      <c r="F56" s="17"/>
+      <c r="G56" s="30"/>
+      <c r="H56" s="31"/>
+      <c r="I56" s="31"/>
+      <c r="J56" s="32"/>
+      <c r="K56" s="33"/>
+    </row>
+    <row r="57" spans="2:11" ht="29.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B57" s="14"/>
+      <c r="C57" s="9"/>
+      <c r="D57" s="9"/>
+      <c r="E57" s="9"/>
+      <c r="F57" s="9"/>
+      <c r="G57" s="10"/>
+      <c r="H57" s="11"/>
+      <c r="I57" s="11"/>
+      <c r="J57" s="12"/>
+      <c r="K57" s="15"/>
+    </row>
+    <row r="58" spans="2:11" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="B58" s="8"/>
+      <c r="C58" s="8"/>
+      <c r="D58" s="8"/>
+      <c r="E58" s="8"/>
+      <c r="F58" s="8"/>
+      <c r="G58" s="8"/>
+      <c r="H58" s="8"/>
+      <c r="I58" s="8"/>
+      <c r="J58" s="8"/>
+      <c r="K58" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="J7:K7"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="D8:D9"/>
-    <mergeCell ref="E8:E9"/>
-    <mergeCell ref="F8:F9"/>
-    <mergeCell ref="G8:H8"/>
-    <mergeCell ref="K8:K9"/>
-    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="J10:K10"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="D11:D12"/>
+    <mergeCell ref="E11:E12"/>
+    <mergeCell ref="F11:F12"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="K11:K12"/>
+    <mergeCell ref="I11:J11"/>
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="48" fitToHeight="0" orientation="portrait" r:id="rId1"/>
+  <pageMargins left="0.47244094488188981" right="0.43307086614173229" top="0.35433070866141736" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup paperSize="9" scale="40" orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/템플릿/토건 명세표 템플릿.xlsx
+++ b/템플릿/토건 명세표 템플릿.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\.shortcut-targets-by-id\1j04MMoet9_yHyMEheShb_L_xq-0Mij5h\3. 온결(신규법인)\ON260901-16101(백지혜, 장성욱, 여의도동 아파트 상속) 정우진\__평가서\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\내 드라이브\02.하이테크\온결(우진)\ON260902-3001(임근실 성남여수동 상속증여 토건) 정우진\__평가서\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{334BBA9A-239B-4A9D-B61D-26BF0B43E4DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE7E2430-9046-465E-820E-7E7F3D7AEC52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" tabRatio="724" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,9 +16,9 @@
     <sheet name="Sheet2" sheetId="4" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet2!$B$3:$J$54</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet2!$B$3:$K$57</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -35,9 +35,121 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="33">
+  <si>
+    <t>일련
+번호</t>
+  </si>
+  <si>
+    <t>소재지</t>
+  </si>
+  <si>
+    <t>지 번</t>
+  </si>
+  <si>
+    <t>지목 및
+용   도</t>
+  </si>
+  <si>
+    <t>용도지역
+및  구조</t>
+  </si>
+  <si>
+    <t>면  적  (㎡)</t>
+  </si>
+  <si>
+    <t>감 정 평 가 액</t>
+  </si>
+  <si>
+    <t>비 고</t>
+  </si>
+  <si>
+    <t>공 부</t>
+  </si>
+  <si>
+    <t>사 정</t>
+  </si>
+  <si>
+    <t>금액(원)</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>여수동</t>
+  </si>
+  <si>
+    <t>457</t>
+  </si>
+  <si>
+    <t>대</t>
+  </si>
+  <si>
+    <t>1종일주</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>가</t>
+  </si>
+  <si>
+    <t>제2종근린생활시</t>
+  </si>
+  <si>
+    <t>철근콘크리트구조</t>
+  </si>
+  <si>
+    <t>설(일반음식점)</t>
+  </si>
+  <si>
+    <t>1층</t>
+  </si>
+  <si>
+    <t>2층</t>
+  </si>
+  <si>
+    <t>3층</t>
+  </si>
+  <si>
+    <t>4층</t>
+  </si>
+  <si>
+    <t>계단,승강기탑</t>
+  </si>
+  <si>
+    <t>옥탑1층</t>
+  </si>
+  <si>
+    <t>합  계</t>
+  </si>
+  <si>
+    <t>다가구주택</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1가구)</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>x 36/50</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">              (토지·건물)감정평가명세표</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>단가(원/㎡)</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="16">
+  <numFmts count="12">
     <numFmt numFmtId="42" formatCode="_-&quot;₩&quot;* #,##0_-;\-&quot;₩&quot;* #,##0_-;_-&quot;₩&quot;* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
@@ -49,13 +161,9 @@
     <numFmt numFmtId="181" formatCode="#,##0.0"/>
     <numFmt numFmtId="182" formatCode="#,##0.00##"/>
     <numFmt numFmtId="183" formatCode="#,##0.00_);[Red]\(#,##0.00\)"/>
-    <numFmt numFmtId="184" formatCode="#,##0.0_);[Red]\(#,##0.0\)"/>
-    <numFmt numFmtId="185" formatCode="#,##0.000_);[Red]\(#,##0.000\)"/>
-    <numFmt numFmtId="186" formatCode="#,##0.0000_);[Red]\(#,##0.0000\)"/>
-    <numFmt numFmtId="187" formatCode="mm&quot;월&quot;\ dd&quot;일&quot;"/>
-    <numFmt numFmtId="193" formatCode="&quot;₩&quot;#,##0"/>
+    <numFmt numFmtId="184" formatCode="&quot;₩&quot;#,##0"/>
   </numFmts>
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -102,14 +210,6 @@
       <charset val="129"/>
     </font>
     <font>
-      <b/>
-      <sz val="14"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="한컴 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
-    </font>
-    <font>
       <sz val="11"/>
       <name val="한컴 고딕"/>
       <family val="3"/>
@@ -143,15 +243,42 @@
       <charset val="129"/>
     </font>
     <font>
-      <b/>
-      <sz val="16"/>
+      <sz val="20"/>
       <name val="한컴 고딕"/>
       <family val="3"/>
       <charset val="129"/>
     </font>
     <font>
       <b/>
-      <sz val="40"/>
+      <sz val="20"/>
+      <name val="한컴 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="22"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="한컴 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="22"/>
+      <name val="한컴 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="24"/>
+      <name val="한컴 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="52"/>
       <name val="한컴 고딕"/>
       <family val="3"/>
       <charset val="129"/>
@@ -395,173 +522,158 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="42" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="41" fontId="9" fillId="0" borderId="0" xfId="17" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="183" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="183" fontId="7" fillId="0" borderId="0" xfId="17" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="7" fillId="0" borderId="0" xfId="17" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="183" fontId="10" fillId="0" borderId="4" xfId="17" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="10" fillId="0" borderId="4" xfId="17" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="11" fillId="0" borderId="4" xfId="20" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="11" fillId="0" borderId="16" xfId="17" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="12" fillId="0" borderId="3" xfId="17" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="12" fillId="0" borderId="3" xfId="17" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="12" fillId="0" borderId="3" xfId="17" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="17" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="183" fontId="12" fillId="3" borderId="3" xfId="17" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="183" fontId="12" fillId="3" borderId="9" xfId="17" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="13" fillId="3" borderId="9" xfId="17" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="183" fontId="12" fillId="0" borderId="3" xfId="17" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="12" fillId="0" borderId="3" xfId="17" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="13" fillId="0" borderId="3" xfId="20" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="13" fillId="0" borderId="9" xfId="17" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="15" fillId="0" borderId="3" xfId="17" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="15" fillId="0" borderId="3" xfId="17" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="15" fillId="0" borderId="3" xfId="17" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" xfId="17" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="15" fillId="0" borderId="9" xfId="17" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="184" fontId="16" fillId="3" borderId="9" xfId="20" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="7" fillId="0" borderId="0" xfId="17" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="41" fontId="10" fillId="0" borderId="0" xfId="17" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="183" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="183" fontId="8" fillId="0" borderId="0" xfId="17" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="8" fillId="0" borderId="0" xfId="17" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="8" fillId="0" borderId="0" xfId="17" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="11" fillId="0" borderId="3" xfId="17" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="11" fillId="0" borderId="3" xfId="17" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="183" fontId="11" fillId="0" borderId="3" xfId="17" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="11" fillId="0" borderId="3" xfId="17" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="186" fontId="11" fillId="0" borderId="3" xfId="17" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="185" fontId="11" fillId="0" borderId="3" xfId="17" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="187" fontId="11" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="184" fontId="11" fillId="0" borderId="3" xfId="17" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="184" fontId="11" fillId="0" borderId="3" xfId="17" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="186" fontId="11" fillId="0" borderId="3" xfId="17" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="11" fillId="0" borderId="3" xfId="17" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="183" fontId="11" fillId="0" borderId="3" xfId="17" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="11" fillId="0" borderId="3" xfId="17" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="12" fillId="0" borderId="3" xfId="20" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="183" fontId="11" fillId="0" borderId="4" xfId="17" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="11" fillId="0" borderId="4" xfId="17" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="12" fillId="0" borderId="4" xfId="20" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="14" fillId="0" borderId="0" xfId="17" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="41" fontId="17" fillId="0" borderId="0" xfId="17" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="17" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="17" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="11" fillId="0" borderId="0" xfId="17" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="12" fillId="0" borderId="9" xfId="17" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="12" fillId="0" borderId="16" xfId="17" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="183" fontId="11" fillId="3" borderId="3" xfId="17" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="193" fontId="13" fillId="3" borderId="9" xfId="20" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="12" fillId="3" borderId="9" xfId="17" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="21">
@@ -606,13 +718,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>890623</xdr:colOff>
-      <xdr:row>50</xdr:row>
+      <xdr:row>53</xdr:row>
       <xdr:rowOff>134235</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>8</xdr:col>
+      <xdr:col>9</xdr:col>
       <xdr:colOff>881658</xdr:colOff>
-      <xdr:row>54</xdr:row>
+      <xdr:row>57</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -701,111 +813,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>36420</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>126092</xdr:rowOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>17463</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>450274</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>207683</xdr:colOff>
-      <xdr:row>39</xdr:row>
-      <xdr:rowOff>145677</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="3" name="자유형: 도형 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7D6B3548-6AAD-49DD-9A53-6814648E86FE}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="6792820" y="6596742"/>
-          <a:ext cx="171263" cy="908585"/>
-        </a:xfrm>
-        <a:custGeom>
-          <a:avLst/>
-          <a:gdLst>
-            <a:gd name="csX0" fmla="*/ 0 w 239485"/>
-            <a:gd name="csY0" fmla="*/ 0 h 656771"/>
-            <a:gd name="csX1" fmla="*/ 239485 w 239485"/>
-            <a:gd name="csY1" fmla="*/ 0 h 656771"/>
-            <a:gd name="csX2" fmla="*/ 239485 w 239485"/>
-            <a:gd name="csY2" fmla="*/ 656771 h 656771"/>
-            <a:gd name="csX3" fmla="*/ 10885 w 239485"/>
-            <a:gd name="csY3" fmla="*/ 656771 h 656771"/>
-          </a:gdLst>
-          <a:ahLst/>
-          <a:cxnLst>
-            <a:cxn ang="0">
-              <a:pos x="csX0" y="csY0"/>
-            </a:cxn>
-            <a:cxn ang="0">
-              <a:pos x="csX1" y="csY1"/>
-            </a:cxn>
-            <a:cxn ang="0">
-              <a:pos x="csX2" y="csY2"/>
-            </a:cxn>
-            <a:cxn ang="0">
-              <a:pos x="csX3" y="csY3"/>
-            </a:cxn>
-          </a:cxnLst>
-          <a:rect l="l" t="t" r="r" b="b"/>
-          <a:pathLst>
-            <a:path w="239485" h="656771">
-              <a:moveTo>
-                <a:pt x="0" y="0"/>
-              </a:moveTo>
-              <a:lnTo>
-                <a:pt x="239485" y="0"/>
-              </a:lnTo>
-              <a:lnTo>
-                <a:pt x="239485" y="656771"/>
-              </a:lnTo>
-              <a:lnTo>
-                <a:pt x="10885" y="656771"/>
-              </a:lnTo>
-            </a:path>
-          </a:pathLst>
-        </a:custGeom>
-        <a:noFill/>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:srgbClr val="000000"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:round/>
-        </a:ln>
-        <a:effectLst/>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr rtlCol="0" anchor="ctr"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>225280</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>34638</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>1085273</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>150089</xdr:rowOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>438729</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>11545</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
@@ -820,8 +837,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="225280" y="427183"/>
-          <a:ext cx="1702811" cy="1616361"/>
+          <a:off x="283008" y="842819"/>
+          <a:ext cx="2372448" cy="2389908"/>
           <a:chOff x="361950" y="806450"/>
           <a:chExt cx="1295400" cy="1217312"/>
         </a:xfrm>
@@ -916,7 +933,7 @@
           <a:p>
             <a:pPr algn="ctr" fontAlgn="base" latinLnBrk="0"/>
             <a:r>
-              <a:rPr lang="en-US" altLang="ko-KR" sz="2800" b="1" kern="0" spc="0">
+              <a:rPr lang="en-US" altLang="ko-KR" sz="3200" b="1" kern="0" spc="0">
                 <a:solidFill>
                   <a:srgbClr val="808080"/>
                 </a:solidFill>
@@ -927,7 +944,7 @@
               <a:t>chapter</a:t>
             </a:r>
             <a:r>
-              <a:rPr lang="en-US" altLang="ko-KR" sz="3200" b="1" kern="0" spc="0">
+              <a:rPr lang="en-US" altLang="ko-KR" sz="3600" b="1" kern="0" spc="0">
                 <a:solidFill>
                   <a:srgbClr val="808080"/>
                 </a:solidFill>
@@ -1000,7 +1017,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:rPr lang="en-US" altLang="ko-KR" sz="6000" b="0">
+              <a:rPr lang="en-US" altLang="ko-KR" sz="7200" b="0">
                 <a:solidFill>
                   <a:schemeClr val="dk1"/>
                 </a:solidFill>
@@ -1011,7 +1028,7 @@
               </a:rPr>
               <a:t>3</a:t>
             </a:r>
-            <a:endParaRPr lang="ko-KR" altLang="ko-KR" sz="4000" b="0">
+            <a:endParaRPr lang="ko-KR" altLang="ko-KR" sz="4800" b="0">
               <a:solidFill>
                 <a:schemeClr val="dk1"/>
               </a:solidFill>
@@ -1029,15 +1046,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>251653</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>76361</xdr:rowOff>
+      <xdr:colOff>690381</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>110998</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>803017</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>76361</xdr:rowOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>1241745</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>110998</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1054,14 +1071,14 @@
       </xdr:nvSpPr>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="2329835" y="1969816"/>
-          <a:ext cx="8460000" cy="0"/>
+          <a:off x="2907108" y="3031998"/>
+          <a:ext cx="12293092" cy="0"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
         </a:prstGeom>
         <a:noFill/>
-        <a:ln w="35941">
+        <a:ln w="57150">
           <a:solidFill>
             <a:srgbClr val="808080"/>
           </a:solidFill>
@@ -1402,691 +1419,728 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B3:J55"/>
+  <dimension ref="B3:K58"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="3.5" style="6" customWidth="1"/>
-    <col min="2" max="2" width="6.75" style="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15" style="6" customWidth="1"/>
-    <col min="4" max="5" width="11" style="6" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="22.5" style="6" customWidth="1"/>
-    <col min="7" max="7" width="17.25" style="6" customWidth="1"/>
-    <col min="8" max="8" width="9.08203125" style="6" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="24.9140625" style="6" customWidth="1"/>
-    <col min="10" max="10" width="11.1640625" style="6" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="6.5" style="6" customWidth="1"/>
-    <col min="12" max="16384" width="8.6640625" style="6"/>
+    <col min="1" max="1" width="3.5" style="1" customWidth="1"/>
+    <col min="2" max="2" width="10.6640625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="15" style="1" customWidth="1"/>
+    <col min="4" max="4" width="11" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="30.4140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.9140625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="15.6640625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="20.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="33.75" style="1" customWidth="1"/>
+    <col min="11" max="11" width="21.1640625" style="1" customWidth="1"/>
+    <col min="12" max="12" width="6.5" style="1" customWidth="1"/>
+    <col min="13" max="16384" width="8.6640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:10" ht="52.5" x14ac:dyDescent="1.25">
-      <c r="C3" s="38"/>
-      <c r="D3" s="38"/>
-      <c r="E3" s="38"/>
-      <c r="F3" s="38"/>
-      <c r="G3" s="38"/>
-      <c r="H3" s="38"/>
-      <c r="I3" s="38"/>
-      <c r="J3" s="38"/>
-    </row>
-    <row r="4" spans="2:10" ht="47.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B4" s="37" t="inlineStr">
-        <is>
-          <t>            (토지·건물)감정평가명세표</t>
-        </is>
-      </c>
-      <c r="G4" s="8"/>
-    </row>
-    <row r="5" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B5" s="7"/>
-      <c r="G5" s="8"/>
-    </row>
-    <row r="6" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B6" s="7"/>
-      <c r="G6" s="8"/>
-    </row>
-    <row r="7" spans="2:10" ht="15.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B7" s="9"/>
-      <c r="C7" s="10"/>
-      <c r="D7" s="9"/>
-      <c r="E7" s="10"/>
-      <c r="F7" s="10"/>
-      <c r="G7" s="11"/>
-      <c r="H7" s="12"/>
-      <c r="I7" s="13"/>
-      <c r="J7" s="13"/>
-    </row>
-    <row r="8" spans="2:10" ht="24.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B8" s="39" t="inlineStr">
-        <is>
-          <t>일련
-번호</t>
-        </is>
-      </c>
-      <c r="C8" s="1" t="inlineStr">
-        <is>
-          <t>소재지</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="inlineStr">
-        <is>
-          <t>지 번</t>
-        </is>
-      </c>
-      <c r="E8" s="1" t="inlineStr">
-        <is>
-          <t>지목 및
-용   도</t>
-        </is>
-      </c>
-      <c r="F8" s="1" t="inlineStr">
-        <is>
-          <t>용도지역
-및  구조</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>면  적  (㎡)</t>
-        </is>
-      </c>
-      <c r="H8" s="3"/>
-      <c r="I8" s="4" t="inlineStr">
-        <is>
-          <t>감 정 평 가 액</t>
-        </is>
-      </c>
-      <c r="J8" s="40" t="inlineStr">
-        <is>
-          <t>비 고</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" spans="2:10" ht="24.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="B9" s="41"/>
-      <c r="C9" s="5"/>
-      <c r="D9" s="5"/>
-      <c r="E9" s="5"/>
-      <c r="F9" s="5"/>
-      <c r="G9" s="4" t="inlineStr">
-        <is>
-          <t>공 부</t>
-        </is>
-      </c>
-      <c r="H9" s="4" t="inlineStr">
-        <is>
-          <t>사 정</t>
-        </is>
-      </c>
-      <c r="I9" s="4" t="inlineStr">
-        <is>
-          <t>금액(원)</t>
-        </is>
-      </c>
-      <c r="J9" s="42"/>
-    </row>
-    <row r="10" spans="2:10" ht="23" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B10" s="43"/>
-      <c r="C10" s="14"/>
-      <c r="D10" s="15"/>
-      <c r="E10" s="15"/>
-      <c r="F10" s="15"/>
-      <c r="G10" s="15"/>
-      <c r="H10" s="15"/>
-      <c r="I10" s="15"/>
+    <row r="3" spans="2:11" ht="52.5" x14ac:dyDescent="1.25">
+      <c r="C3" s="13"/>
+      <c r="D3" s="13"/>
+      <c r="E3" s="13"/>
+      <c r="F3" s="13"/>
+      <c r="G3" s="13"/>
+      <c r="H3" s="13"/>
+      <c r="I3" s="13"/>
+      <c r="J3" s="13"/>
+      <c r="K3" s="13"/>
+    </row>
+    <row r="4" spans="2:11" ht="47.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="G4" s="3"/>
+    </row>
+    <row r="5" spans="2:11" ht="68" x14ac:dyDescent="0.4">
+      <c r="B5" s="53" t="s">
+        <v>31</v>
+      </c>
+      <c r="G5" s="3"/>
+    </row>
+    <row r="6" spans="2:11" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B6" s="2"/>
+      <c r="G6" s="3"/>
+    </row>
+    <row r="7" spans="2:11" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B7" s="2"/>
+      <c r="G7" s="3"/>
+    </row>
+    <row r="8" spans="2:11" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B8" s="2"/>
+      <c r="G8" s="3"/>
+    </row>
+    <row r="9" spans="2:11" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B9" s="2"/>
+      <c r="G9" s="3"/>
+    </row>
+    <row r="10" spans="2:11" ht="15.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B10" s="4"/>
+      <c r="C10" s="5"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="5"/>
+      <c r="F10" s="5"/>
+      <c r="G10" s="6"/>
+      <c r="H10" s="7"/>
+      <c r="I10" s="7"/>
       <c r="J10" s="44"/>
-    </row>
-    <row r="11" spans="2:10" ht="23" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B11" s="43" t="inlineStr">
+      <c r="K10" s="44"/>
+    </row>
+    <row r="11" spans="2:11" ht="45.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B11" s="45" t="s">
+        <v>0</v>
+      </c>
+      <c r="C11" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="D11" s="47" t="s">
+        <v>2</v>
+      </c>
+      <c r="E11" s="47" t="s">
+        <v>3</v>
+      </c>
+      <c r="F11" s="47" t="s">
+        <v>4</v>
+      </c>
+      <c r="G11" s="49" t="s">
+        <v>5</v>
+      </c>
+      <c r="H11" s="50"/>
+      <c r="I11" s="49" t="s">
+        <v>6</v>
+      </c>
+      <c r="J11" s="50"/>
+      <c r="K11" s="51" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="2:11" ht="48" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
+      <c r="B12" s="46"/>
+      <c r="C12" s="48"/>
+      <c r="D12" s="48"/>
+      <c r="E12" s="48"/>
+      <c r="F12" s="48"/>
+      <c r="G12" s="34" t="s">
+        <v>8</v>
+      </c>
+      <c r="H12" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="I12" s="34" t="s">
+        <v>32</v>
+      </c>
+      <c r="J12" s="34" t="s">
+        <v>10</v>
+      </c>
+      <c r="K12" s="52"/>
+    </row>
+    <row r="13" spans="2:11" ht="29.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B13" s="35"/>
+      <c r="C13" s="36"/>
+      <c r="D13" s="37"/>
+      <c r="E13" s="37"/>
+      <c r="F13" s="36"/>
+      <c r="G13" s="38"/>
+      <c r="H13" s="38"/>
+      <c r="I13" s="39"/>
+      <c r="J13" s="40"/>
+      <c r="K13" s="41"/>
+    </row>
+    <row r="14" spans="2:11" ht="29.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B14" s="35" t="inlineStr">
         <is>
           <t>{{명세_기호}}</t>
         </is>
       </c>
-      <c r="C11" s="14" t="inlineStr">
+      <c r="C14" s="36" t="inlineStr">
         <is>
           <t>{{명세_소재지}}</t>
         </is>
       </c>
-      <c r="D11" s="15" t="inlineStr">
+      <c r="D14" s="37" t="inlineStr">
         <is>
           <t>{{명세_지번}}</t>
         </is>
       </c>
-      <c r="E11" s="15" t="inlineStr">
+      <c r="E14" s="37" t="inlineStr">
         <is>
           <t>{{명세_지목용도}}</t>
         </is>
       </c>
-      <c r="F11" s="14" t="inlineStr">
+      <c r="F14" s="36" t="inlineStr">
         <is>
           <t>{{명세_지역구조}}</t>
         </is>
       </c>
-      <c r="G11" s="16" t="inlineStr">
+      <c r="G14" s="38" t="inlineStr">
         <is>
           <t>{{명세_공부면적}}</t>
         </is>
       </c>
-      <c r="H11" s="16" t="inlineStr">
+      <c r="H14" s="38" t="inlineStr">
         <is>
           <t>{{명세_사정면적}}</t>
         </is>
       </c>
-      <c r="I11" s="17" t="inlineStr">
+      <c r="I14" s="39" t="inlineStr">
         <is>
-          <t>{{명세_평가액}}</t>
+          <t>{{명세_단가}}</t>
         </is>
       </c>
-      <c r="J11" s="44" t="inlineStr">
+      <c r="J14" s="40">
+        <f>+I14*H14</f>
+      </c>
+      <c r="K14" s="42" t="inlineStr">
         <is>
           <t>{{명세_비고}}</t>
         </is>
       </c>
     </row>
-    <row r="12" spans="2:10" ht="23" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B12" s="43"/>
-      <c r="C12" s="14"/>
-      <c r="D12" s="15"/>
-      <c r="E12" s="15"/>
-      <c r="F12" s="14"/>
-      <c r="G12" s="18"/>
-      <c r="H12" s="19"/>
-      <c r="I12" s="17"/>
-      <c r="J12" s="44"/>
-    </row>
-    <row r="13" spans="2:10" ht="23" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B13" s="43"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="15"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="14"/>
-      <c r="G13" s="20"/>
-      <c r="H13" s="19"/>
-      <c r="I13" s="17"/>
-      <c r="J13" s="44"/>
-    </row>
-    <row r="14" spans="2:10" ht="23" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B14" s="43"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="15"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="15"/>
-      <c r="G14" s="20"/>
-      <c r="H14" s="19"/>
-      <c r="I14" s="17"/>
-      <c r="J14" s="44"/>
-    </row>
-    <row r="15" spans="2:10" ht="23" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B15" s="43"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="15"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="45"/>
-      <c r="G15" s="20"/>
-      <c r="H15" s="19"/>
-      <c r="I15" s="17"/>
-      <c r="J15" s="44"/>
-    </row>
-    <row r="16" spans="2:10" ht="23" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B16" s="43"/>
-      <c r="C16" s="14"/>
-      <c r="D16" s="15"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="15"/>
-      <c r="G16" s="20"/>
-      <c r="H16" s="19"/>
-      <c r="I16" s="17"/>
-      <c r="J16" s="44"/>
-    </row>
-    <row r="17" spans="2:10" ht="23" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B17" s="43"/>
-      <c r="C17" s="14"/>
-      <c r="D17" s="14"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="14"/>
-      <c r="G17" s="18"/>
-      <c r="H17" s="20"/>
-      <c r="I17" s="17"/>
-      <c r="J17" s="44"/>
-    </row>
-    <row r="18" spans="2:10" ht="23" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B18" s="43"/>
-      <c r="C18" s="14"/>
-      <c r="D18" s="14"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="14"/>
-      <c r="G18" s="21"/>
-      <c r="H18" s="20"/>
-      <c r="I18" s="17"/>
-      <c r="J18" s="44"/>
-    </row>
-    <row r="19" spans="2:10" ht="23" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B19" s="43"/>
-      <c r="C19" s="14"/>
-      <c r="D19" s="14"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="14"/>
-      <c r="G19" s="21"/>
-      <c r="H19" s="20"/>
-      <c r="I19" s="17"/>
-      <c r="J19" s="44"/>
-    </row>
-    <row r="20" spans="2:10" ht="23" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B20" s="43"/>
-      <c r="C20" s="14"/>
-      <c r="D20" s="14"/>
-      <c r="E20" s="14"/>
-      <c r="F20" s="14"/>
-      <c r="G20" s="21"/>
-      <c r="H20" s="20"/>
-      <c r="I20" s="17"/>
-      <c r="J20" s="44"/>
-    </row>
-    <row r="21" spans="2:10" ht="23" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B21" s="43"/>
-      <c r="C21" s="14"/>
-      <c r="D21" s="14"/>
-      <c r="E21" s="14"/>
-      <c r="F21" s="14"/>
-      <c r="G21" s="21"/>
-      <c r="H21" s="20"/>
-      <c r="I21" s="17"/>
-      <c r="J21" s="44"/>
-    </row>
-    <row r="22" spans="2:10" ht="23" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B22" s="43"/>
-      <c r="C22" s="22"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="14"/>
-      <c r="G22" s="21"/>
-      <c r="H22" s="20"/>
-      <c r="I22" s="17"/>
-      <c r="J22" s="44"/>
-    </row>
-    <row r="23" spans="2:10" ht="23" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B23" s="43"/>
-      <c r="C23" s="22"/>
-      <c r="D23" s="14"/>
-      <c r="E23" s="14"/>
-      <c r="F23" s="14"/>
-      <c r="G23" s="21"/>
-      <c r="H23" s="20"/>
-      <c r="I23" s="17"/>
-      <c r="J23" s="44"/>
-    </row>
-    <row r="24" spans="2:10" ht="23" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B24" s="43"/>
-      <c r="C24" s="14"/>
-      <c r="D24" s="14"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="21"/>
-      <c r="H24" s="20"/>
-      <c r="I24" s="17"/>
-      <c r="J24" s="44"/>
-    </row>
-    <row r="25" spans="2:10" ht="23" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B25" s="46"/>
-      <c r="C25" s="14"/>
-      <c r="D25" s="23"/>
-      <c r="E25" s="14"/>
-      <c r="F25" s="14"/>
-      <c r="G25" s="24"/>
-      <c r="H25" s="20"/>
-      <c r="I25" s="17"/>
-      <c r="J25" s="44"/>
-    </row>
-    <row r="26" spans="2:10" ht="23" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B26" s="46"/>
-      <c r="C26" s="14"/>
-      <c r="D26" s="23"/>
-      <c r="E26" s="14"/>
-      <c r="F26" s="14"/>
-      <c r="G26" s="24"/>
-      <c r="H26" s="20"/>
-      <c r="I26" s="17"/>
-      <c r="J26" s="44"/>
-    </row>
-    <row r="27" spans="2:10" ht="23" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B27" s="46"/>
-      <c r="C27" s="14"/>
-      <c r="D27" s="23"/>
-      <c r="E27" s="14"/>
-      <c r="F27" s="14"/>
-      <c r="G27" s="24"/>
-      <c r="H27" s="20"/>
-      <c r="I27" s="17"/>
-      <c r="J27" s="44"/>
-    </row>
-    <row r="28" spans="2:10" ht="23" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B28" s="46"/>
-      <c r="C28" s="14"/>
-      <c r="D28" s="23"/>
-      <c r="E28" s="14"/>
-      <c r="F28" s="14"/>
-      <c r="G28" s="24"/>
-      <c r="H28" s="20"/>
-      <c r="I28" s="17"/>
-      <c r="J28" s="44"/>
-    </row>
-    <row r="29" spans="2:10" ht="23" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B29" s="46"/>
-      <c r="C29" s="14"/>
-      <c r="D29" s="23"/>
-      <c r="E29" s="14"/>
-      <c r="F29" s="14"/>
-      <c r="G29" s="24"/>
-      <c r="H29" s="20"/>
-      <c r="I29" s="17"/>
-      <c r="J29" s="44"/>
-    </row>
-    <row r="30" spans="2:10" ht="23" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B30" s="46"/>
-      <c r="C30" s="14"/>
-      <c r="D30" s="23"/>
-      <c r="E30" s="14"/>
-      <c r="F30" s="14"/>
-      <c r="G30" s="24"/>
-      <c r="H30" s="20"/>
-      <c r="I30" s="17"/>
-      <c r="J30" s="44"/>
-    </row>
-    <row r="31" spans="2:10" ht="23" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B31" s="43"/>
-      <c r="C31" s="14"/>
-      <c r="D31" s="14"/>
-      <c r="E31" s="14"/>
-      <c r="F31" s="14"/>
-      <c r="G31" s="16"/>
-      <c r="H31" s="18"/>
-      <c r="I31" s="17"/>
-      <c r="J31" s="44"/>
-    </row>
-    <row r="32" spans="2:10" ht="23" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B32" s="43"/>
-      <c r="C32" s="14"/>
-      <c r="D32" s="14"/>
-      <c r="E32" s="14"/>
-      <c r="F32" s="14"/>
-      <c r="G32" s="16"/>
-      <c r="H32" s="18"/>
-      <c r="I32" s="17"/>
-      <c r="J32" s="44"/>
-    </row>
-    <row r="33" spans="2:10" ht="23" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B33" s="43"/>
-      <c r="C33" s="14"/>
-      <c r="D33" s="14"/>
-      <c r="E33" s="14"/>
-      <c r="F33" s="14"/>
-      <c r="G33" s="16"/>
-      <c r="H33" s="18"/>
-      <c r="I33" s="17"/>
-      <c r="J33" s="44"/>
-    </row>
-    <row r="34" spans="2:10" ht="23" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B34" s="43"/>
-      <c r="C34" s="14"/>
-      <c r="D34" s="14"/>
-      <c r="E34" s="14"/>
-      <c r="F34" s="14"/>
-      <c r="G34" s="18"/>
-      <c r="H34" s="18"/>
-      <c r="I34" s="17"/>
-      <c r="J34" s="47"/>
-    </row>
-    <row r="35" spans="2:10" ht="23" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B35" s="43"/>
-      <c r="C35" s="14"/>
-      <c r="D35" s="14"/>
-      <c r="E35" s="14"/>
-      <c r="F35" s="14"/>
-      <c r="G35" s="16"/>
-      <c r="H35" s="18"/>
-      <c r="I35" s="17"/>
-      <c r="J35" s="47"/>
-    </row>
-    <row r="36" spans="2:10" ht="23" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B36" s="43"/>
-      <c r="C36" s="14"/>
-      <c r="D36" s="14"/>
-      <c r="E36" s="14"/>
-      <c r="F36" s="14"/>
-      <c r="G36" s="16"/>
-      <c r="H36" s="18"/>
-      <c r="I36" s="17"/>
-      <c r="J36" s="47"/>
-    </row>
-    <row r="37" spans="2:10" ht="23" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B37" s="43"/>
-      <c r="C37" s="14"/>
-      <c r="D37" s="14"/>
-      <c r="E37" s="14"/>
-      <c r="F37" s="14"/>
-      <c r="G37" s="16"/>
-      <c r="H37" s="18"/>
-      <c r="I37" s="17"/>
-      <c r="J37" s="47"/>
-    </row>
-    <row r="38" spans="2:10" ht="23" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B38" s="43"/>
-      <c r="C38" s="14"/>
-      <c r="D38" s="14"/>
-      <c r="E38" s="14"/>
-      <c r="F38" s="14"/>
-      <c r="G38" s="16"/>
-      <c r="H38" s="18"/>
-      <c r="I38" s="48"/>
-      <c r="J38" s="47"/>
-    </row>
-    <row r="39" spans="2:10" ht="23" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B39" s="43"/>
-      <c r="C39" s="14"/>
-      <c r="D39" s="14"/>
-      <c r="E39" s="14"/>
-      <c r="F39" s="14"/>
-      <c r="G39" s="18"/>
-      <c r="H39" s="18"/>
-      <c r="I39" s="49"/>
-      <c r="J39" s="44"/>
-    </row>
-    <row r="40" spans="2:10" ht="23" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B40" s="43"/>
-      <c r="C40" s="14"/>
-      <c r="D40" s="50"/>
-      <c r="E40" s="15"/>
-      <c r="F40" s="14"/>
-      <c r="G40" s="16"/>
-      <c r="H40" s="18"/>
-      <c r="I40" s="17"/>
-      <c r="J40" s="44"/>
-    </row>
-    <row r="41" spans="2:10" ht="23" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B41" s="43"/>
-      <c r="C41" s="14"/>
-      <c r="D41" s="15"/>
-      <c r="E41" s="15"/>
-      <c r="F41" s="14"/>
-      <c r="G41" s="24"/>
-      <c r="H41" s="21"/>
-      <c r="I41" s="17"/>
-      <c r="J41" s="44"/>
-    </row>
-    <row r="42" spans="2:10" ht="23" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B42" s="43"/>
-      <c r="C42" s="14"/>
-      <c r="D42" s="15"/>
-      <c r="E42" s="14"/>
-      <c r="F42" s="14"/>
-      <c r="G42" s="14"/>
-      <c r="H42" s="14"/>
-      <c r="I42" s="14"/>
-      <c r="J42" s="44"/>
-    </row>
-    <row r="43" spans="2:10" ht="23" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B43" s="43"/>
-      <c r="C43" s="14"/>
-      <c r="D43" s="15"/>
-      <c r="E43" s="14"/>
-      <c r="F43" s="14"/>
-      <c r="G43" s="14"/>
-      <c r="H43" s="14"/>
-      <c r="I43" s="14"/>
-      <c r="J43" s="44"/>
-    </row>
-    <row r="44" spans="2:10" ht="23" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B44" s="43"/>
-      <c r="C44" s="14"/>
-      <c r="D44" s="15"/>
-      <c r="E44" s="14"/>
-      <c r="F44" s="14"/>
-      <c r="G44" s="14"/>
-      <c r="H44" s="14"/>
-      <c r="I44" s="14"/>
-      <c r="J44" s="44"/>
-    </row>
-    <row r="45" spans="2:10" ht="23" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B45" s="43"/>
-      <c r="C45" s="14"/>
-      <c r="D45" s="15"/>
-      <c r="E45" s="14"/>
-      <c r="F45" s="14"/>
-      <c r="G45" s="14"/>
-      <c r="H45" s="14"/>
-      <c r="I45" s="14"/>
-      <c r="J45" s="44"/>
-    </row>
-    <row r="46" spans="2:10" ht="23" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B46" s="43"/>
-      <c r="C46" s="14"/>
-      <c r="D46" s="14"/>
-      <c r="E46" s="14"/>
-      <c r="F46" s="26"/>
-      <c r="G46" s="27"/>
-      <c r="H46" s="28"/>
-      <c r="I46" s="29"/>
-      <c r="J46" s="51"/>
-    </row>
-    <row r="47" spans="2:10" ht="23" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B47" s="43"/>
-      <c r="C47" s="14"/>
-      <c r="D47" s="14"/>
-      <c r="E47" s="14"/>
-      <c r="F47" s="26"/>
-      <c r="G47" s="27"/>
-      <c r="H47" s="28"/>
-      <c r="I47" s="29"/>
-      <c r="J47" s="51"/>
-    </row>
-    <row r="48" spans="2:10" ht="23" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B48" s="43"/>
-      <c r="C48" s="14"/>
-      <c r="D48" s="14"/>
-      <c r="E48" s="14"/>
-      <c r="F48" s="26"/>
-      <c r="G48" s="27"/>
-      <c r="H48" s="28"/>
-      <c r="I48" s="29"/>
-      <c r="J48" s="51"/>
-    </row>
-    <row r="49" spans="2:10" ht="23" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B49" s="43"/>
-      <c r="C49" s="14"/>
-      <c r="D49" s="14"/>
-      <c r="E49" s="14"/>
-      <c r="F49" s="26"/>
-      <c r="G49" s="27"/>
-      <c r="H49" s="28"/>
-      <c r="I49" s="29"/>
-      <c r="J49" s="51"/>
-    </row>
-    <row r="50" spans="2:10" ht="23" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B50" s="55"/>
-      <c r="C50" s="56" t="inlineStr">
-        <is>
-          <t>합  계</t>
-        </is>
-      </c>
-      <c r="D50" s="57"/>
-      <c r="E50" s="57"/>
-      <c r="F50" s="57"/>
-      <c r="G50" s="58"/>
-      <c r="H50" s="58"/>
-      <c r="I50" s="59">
-        <f>SUM(I11:I45)</f>
-        <v>1400000000</v>
-      </c>
-      <c r="J50" s="60"/>
-    </row>
-    <row r="51" spans="2:10" ht="23" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B51" s="46"/>
-      <c r="C51" s="14"/>
-      <c r="D51" s="14"/>
-      <c r="E51" s="14"/>
-      <c r="F51" s="14"/>
-      <c r="G51" s="30"/>
-      <c r="H51" s="31"/>
-      <c r="I51" s="32"/>
-      <c r="J51" s="52"/>
-    </row>
-    <row r="52" spans="2:10" ht="23" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B52" s="46"/>
-      <c r="C52" s="14"/>
-      <c r="D52" s="14"/>
-      <c r="E52" s="14"/>
-      <c r="F52" s="14"/>
-      <c r="G52" s="30"/>
-      <c r="H52" s="31"/>
-      <c r="I52" s="32"/>
-      <c r="J52" s="52"/>
-    </row>
-    <row r="53" spans="2:10" ht="23" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B53" s="46"/>
-      <c r="C53" s="14"/>
-      <c r="D53" s="14"/>
-      <c r="E53" s="14"/>
-      <c r="F53" s="14"/>
-      <c r="G53" s="30"/>
-      <c r="H53" s="31"/>
-      <c r="I53" s="32"/>
-      <c r="J53" s="52"/>
-    </row>
-    <row r="54" spans="2:10" ht="23" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B54" s="53"/>
-      <c r="C54" s="33"/>
-      <c r="D54" s="33"/>
-      <c r="E54" s="33"/>
-      <c r="F54" s="33"/>
-      <c r="G54" s="34"/>
-      <c r="H54" s="35"/>
-      <c r="I54" s="36"/>
-      <c r="J54" s="54"/>
-    </row>
-    <row r="55" spans="2:10" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="B55" s="25"/>
-      <c r="C55" s="25"/>
-      <c r="D55" s="25"/>
-      <c r="E55" s="25"/>
-      <c r="F55" s="25"/>
-      <c r="G55" s="25"/>
-      <c r="H55" s="25"/>
-      <c r="I55" s="25"/>
-      <c r="J55" s="25"/>
+    <row r="15" spans="2:11" ht="29.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B15" s="35"/>
+      <c r="C15" s="36"/>
+      <c r="D15" s="37"/>
+      <c r="E15" s="37"/>
+      <c r="F15" s="36"/>
+      <c r="G15" s="38"/>
+      <c r="H15" s="38"/>
+      <c r="I15" s="38"/>
+      <c r="J15" s="40"/>
+      <c r="K15" s="41"/>
+    </row>
+    <row r="16" spans="2:11" ht="29.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B16" s="35"/>
+      <c r="C16" s="36"/>
+      <c r="D16" s="37"/>
+      <c r="E16" s="37"/>
+      <c r="F16" s="36"/>
+      <c r="G16" s="38"/>
+      <c r="H16" s="38"/>
+      <c r="I16" s="39"/>
+      <c r="J16" s="40"/>
+      <c r="K16" s="41"/>
+    </row>
+    <row r="17" spans="2:11" ht="29.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B17" s="35"/>
+      <c r="C17" s="36"/>
+      <c r="D17" s="37"/>
+      <c r="E17" s="37"/>
+      <c r="F17" s="36"/>
+      <c r="G17" s="38"/>
+      <c r="H17" s="38"/>
+      <c r="I17" s="39"/>
+      <c r="J17" s="40"/>
+      <c r="K17" s="41"/>
+    </row>
+    <row r="18" spans="2:11" ht="29.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B18" s="35"/>
+      <c r="C18" s="36"/>
+      <c r="D18" s="37"/>
+      <c r="E18" s="37"/>
+      <c r="F18" s="36"/>
+      <c r="G18" s="38"/>
+      <c r="H18" s="38"/>
+      <c r="I18" s="39"/>
+      <c r="J18" s="40"/>
+      <c r="K18" s="42"/>
+    </row>
+    <row r="19" spans="2:11" ht="29.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B19" s="35"/>
+      <c r="C19" s="36"/>
+      <c r="D19" s="37"/>
+      <c r="E19" s="37"/>
+      <c r="F19" s="36"/>
+      <c r="G19" s="38"/>
+      <c r="H19" s="38"/>
+      <c r="I19" s="39"/>
+      <c r="J19" s="40"/>
+      <c r="K19" s="41"/>
+    </row>
+    <row r="20" spans="2:11" ht="29.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B20" s="35"/>
+      <c r="C20" s="36"/>
+      <c r="D20" s="37"/>
+      <c r="E20" s="37"/>
+      <c r="F20" s="36"/>
+      <c r="G20" s="38"/>
+      <c r="H20" s="38"/>
+      <c r="I20" s="39"/>
+      <c r="J20" s="40"/>
+      <c r="K20" s="41"/>
+    </row>
+    <row r="21" spans="2:11" ht="29.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B21" s="35"/>
+      <c r="C21" s="36"/>
+      <c r="D21" s="37"/>
+      <c r="E21" s="37"/>
+      <c r="F21" s="36"/>
+      <c r="G21" s="38"/>
+      <c r="H21" s="38"/>
+      <c r="I21" s="39"/>
+      <c r="J21" s="40"/>
+      <c r="K21" s="41"/>
+    </row>
+    <row r="22" spans="2:11" ht="29.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B22" s="35"/>
+      <c r="C22" s="36"/>
+      <c r="D22" s="37"/>
+      <c r="E22" s="37"/>
+      <c r="F22" s="36"/>
+      <c r="G22" s="38"/>
+      <c r="H22" s="38"/>
+      <c r="I22" s="39"/>
+      <c r="J22" s="40"/>
+      <c r="K22" s="42"/>
+    </row>
+    <row r="23" spans="2:11" ht="29.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B23" s="35"/>
+      <c r="C23" s="36"/>
+      <c r="D23" s="37"/>
+      <c r="E23" s="37"/>
+      <c r="F23" s="36"/>
+      <c r="G23" s="38"/>
+      <c r="H23" s="38"/>
+      <c r="I23" s="39"/>
+      <c r="J23" s="40"/>
+      <c r="K23" s="41"/>
+    </row>
+    <row r="24" spans="2:11" ht="29.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B24" s="35"/>
+      <c r="C24" s="36"/>
+      <c r="D24" s="37"/>
+      <c r="E24" s="37"/>
+      <c r="F24" s="36"/>
+      <c r="G24" s="38"/>
+      <c r="H24" s="38"/>
+      <c r="I24" s="39"/>
+      <c r="J24" s="40"/>
+      <c r="K24" s="41"/>
+    </row>
+    <row r="25" spans="2:11" ht="29.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B25" s="35"/>
+      <c r="C25" s="36"/>
+      <c r="D25" s="37"/>
+      <c r="E25" s="37"/>
+      <c r="F25" s="36"/>
+      <c r="G25" s="38"/>
+      <c r="H25" s="38"/>
+      <c r="I25" s="39"/>
+      <c r="J25" s="40"/>
+      <c r="K25" s="41"/>
+    </row>
+    <row r="26" spans="2:11" ht="29.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B26" s="35"/>
+      <c r="C26" s="36"/>
+      <c r="D26" s="37"/>
+      <c r="E26" s="37"/>
+      <c r="F26" s="36"/>
+      <c r="G26" s="38"/>
+      <c r="H26" s="38"/>
+      <c r="I26" s="39"/>
+      <c r="J26" s="40"/>
+      <c r="K26" s="42"/>
+    </row>
+    <row r="27" spans="2:11" ht="29.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B27" s="35"/>
+      <c r="C27" s="36"/>
+      <c r="D27" s="37"/>
+      <c r="E27" s="37"/>
+      <c r="F27" s="36"/>
+      <c r="G27" s="38"/>
+      <c r="H27" s="38"/>
+      <c r="I27" s="39"/>
+      <c r="J27" s="40"/>
+      <c r="K27" s="41"/>
+    </row>
+    <row r="28" spans="2:11" ht="29.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B28" s="35"/>
+      <c r="C28" s="36"/>
+      <c r="D28" s="37"/>
+      <c r="E28" s="37"/>
+      <c r="F28" s="36"/>
+      <c r="G28" s="38"/>
+      <c r="H28" s="38"/>
+      <c r="I28" s="39"/>
+      <c r="J28" s="40"/>
+      <c r="K28" s="41"/>
+    </row>
+    <row r="29" spans="2:11" ht="29.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B29" s="35"/>
+      <c r="C29" s="36"/>
+      <c r="D29" s="37"/>
+      <c r="E29" s="37"/>
+      <c r="F29" s="36"/>
+      <c r="G29" s="38"/>
+      <c r="H29" s="38"/>
+      <c r="I29" s="39"/>
+      <c r="J29" s="40"/>
+      <c r="K29" s="41"/>
+    </row>
+    <row r="30" spans="2:11" ht="29.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B30" s="35"/>
+      <c r="C30" s="36"/>
+      <c r="D30" s="37"/>
+      <c r="E30" s="37"/>
+      <c r="F30" s="36"/>
+      <c r="G30" s="38"/>
+      <c r="H30" s="38"/>
+      <c r="I30" s="39"/>
+      <c r="J30" s="40"/>
+      <c r="K30" s="42"/>
+    </row>
+    <row r="31" spans="2:11" ht="29.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B31" s="35"/>
+      <c r="C31" s="36"/>
+      <c r="D31" s="37"/>
+      <c r="E31" s="37"/>
+      <c r="F31" s="36"/>
+      <c r="G31" s="38"/>
+      <c r="H31" s="38"/>
+      <c r="I31" s="39"/>
+      <c r="J31" s="40"/>
+      <c r="K31" s="41"/>
+    </row>
+    <row r="32" spans="2:11" ht="29.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B32" s="35"/>
+      <c r="C32" s="36"/>
+      <c r="D32" s="37"/>
+      <c r="E32" s="37"/>
+      <c r="F32" s="36"/>
+      <c r="G32" s="38"/>
+      <c r="H32" s="38"/>
+      <c r="I32" s="39"/>
+      <c r="J32" s="40"/>
+      <c r="K32" s="41"/>
+    </row>
+    <row r="33" spans="2:11" ht="29.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B33" s="35"/>
+      <c r="C33" s="36"/>
+      <c r="D33" s="37"/>
+      <c r="E33" s="37"/>
+      <c r="F33" s="36"/>
+      <c r="G33" s="38"/>
+      <c r="H33" s="38"/>
+      <c r="I33" s="39"/>
+      <c r="J33" s="40"/>
+      <c r="K33" s="41"/>
+    </row>
+    <row r="34" spans="2:11" ht="29.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B34" s="35"/>
+      <c r="C34" s="36"/>
+      <c r="D34" s="37"/>
+      <c r="E34" s="37"/>
+      <c r="F34" s="36"/>
+      <c r="G34" s="38"/>
+      <c r="H34" s="38"/>
+      <c r="I34" s="39"/>
+      <c r="J34" s="40"/>
+      <c r="K34" s="42"/>
+    </row>
+    <row r="35" spans="2:11" ht="29.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B35" s="35"/>
+      <c r="C35" s="36"/>
+      <c r="D35" s="37"/>
+      <c r="E35" s="37"/>
+      <c r="F35" s="36"/>
+      <c r="G35" s="38"/>
+      <c r="H35" s="38"/>
+      <c r="I35" s="39"/>
+      <c r="J35" s="40"/>
+      <c r="K35" s="41"/>
+    </row>
+    <row r="36" spans="2:11" ht="29.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B36" s="35"/>
+      <c r="C36" s="36"/>
+      <c r="D36" s="37"/>
+      <c r="E36" s="37"/>
+      <c r="F36" s="36"/>
+      <c r="G36" s="38"/>
+      <c r="H36" s="38"/>
+      <c r="I36" s="39"/>
+      <c r="J36" s="40"/>
+      <c r="K36" s="41"/>
+    </row>
+    <row r="37" spans="2:11" ht="29.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B37" s="16"/>
+      <c r="C37" s="17"/>
+      <c r="D37" s="18"/>
+      <c r="E37" s="18"/>
+      <c r="F37" s="17"/>
+      <c r="G37" s="19"/>
+      <c r="H37" s="19"/>
+      <c r="I37" s="20"/>
+      <c r="J37" s="21"/>
+      <c r="K37" s="22"/>
+    </row>
+    <row r="38" spans="2:11" ht="29.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B38" s="16"/>
+      <c r="C38" s="17"/>
+      <c r="D38" s="18"/>
+      <c r="E38" s="18"/>
+      <c r="F38" s="17"/>
+      <c r="G38" s="19"/>
+      <c r="H38" s="19"/>
+      <c r="I38" s="20"/>
+      <c r="J38" s="21"/>
+      <c r="K38" s="22"/>
+    </row>
+    <row r="39" spans="2:11" ht="29.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B39" s="16"/>
+      <c r="C39" s="17"/>
+      <c r="D39" s="18"/>
+      <c r="E39" s="18"/>
+      <c r="F39" s="17"/>
+      <c r="G39" s="19"/>
+      <c r="H39" s="19"/>
+      <c r="I39" s="20"/>
+      <c r="J39" s="21"/>
+      <c r="K39" s="22"/>
+    </row>
+    <row r="40" spans="2:11" ht="29.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B40" s="16"/>
+      <c r="C40" s="17"/>
+      <c r="D40" s="18"/>
+      <c r="E40" s="18"/>
+      <c r="F40" s="17"/>
+      <c r="G40" s="19"/>
+      <c r="H40" s="19"/>
+      <c r="I40" s="20"/>
+      <c r="J40" s="21"/>
+      <c r="K40" s="22"/>
+    </row>
+    <row r="41" spans="2:11" ht="29.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B41" s="16"/>
+      <c r="C41" s="17"/>
+      <c r="D41" s="18"/>
+      <c r="E41" s="18"/>
+      <c r="F41" s="17"/>
+      <c r="G41" s="19"/>
+      <c r="H41" s="19"/>
+      <c r="I41" s="20"/>
+      <c r="J41" s="21"/>
+      <c r="K41" s="22"/>
+    </row>
+    <row r="42" spans="2:11" ht="29.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B42" s="16"/>
+      <c r="C42" s="17"/>
+      <c r="D42" s="18"/>
+      <c r="E42" s="18"/>
+      <c r="F42" s="17"/>
+      <c r="G42" s="19"/>
+      <c r="H42" s="19"/>
+      <c r="I42" s="20"/>
+      <c r="J42" s="21"/>
+      <c r="K42" s="22"/>
+    </row>
+    <row r="43" spans="2:11" ht="29.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B43" s="16"/>
+      <c r="C43" s="17"/>
+      <c r="D43" s="18"/>
+      <c r="E43" s="18"/>
+      <c r="F43" s="17"/>
+      <c r="G43" s="19"/>
+      <c r="H43" s="19"/>
+      <c r="I43" s="20"/>
+      <c r="J43" s="21"/>
+      <c r="K43" s="22"/>
+    </row>
+    <row r="44" spans="2:11" ht="29.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B44" s="16"/>
+      <c r="C44" s="17"/>
+      <c r="D44" s="18"/>
+      <c r="E44" s="18"/>
+      <c r="F44" s="17"/>
+      <c r="G44" s="19"/>
+      <c r="H44" s="19"/>
+      <c r="I44" s="20"/>
+      <c r="J44" s="21"/>
+      <c r="K44" s="22"/>
+    </row>
+    <row r="45" spans="2:11" ht="29.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B45" s="16"/>
+      <c r="C45" s="17"/>
+      <c r="D45" s="18"/>
+      <c r="E45" s="18"/>
+      <c r="F45" s="17"/>
+      <c r="G45" s="19"/>
+      <c r="H45" s="19"/>
+      <c r="I45" s="19"/>
+      <c r="J45" s="21"/>
+      <c r="K45" s="22"/>
+    </row>
+    <row r="46" spans="2:11" ht="29.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B46" s="16"/>
+      <c r="C46" s="17"/>
+      <c r="D46" s="18"/>
+      <c r="E46" s="18"/>
+      <c r="F46" s="17"/>
+      <c r="G46" s="19"/>
+      <c r="H46" s="19"/>
+      <c r="I46" s="19"/>
+      <c r="J46" s="21"/>
+      <c r="K46" s="22"/>
+    </row>
+    <row r="47" spans="2:11" ht="29.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B47" s="16"/>
+      <c r="C47" s="17"/>
+      <c r="D47" s="18"/>
+      <c r="E47" s="18"/>
+      <c r="F47" s="17"/>
+      <c r="G47" s="19"/>
+      <c r="H47" s="19"/>
+      <c r="I47" s="19"/>
+      <c r="J47" s="21"/>
+      <c r="K47" s="22"/>
+    </row>
+    <row r="48" spans="2:11" ht="29.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B48" s="16"/>
+      <c r="C48" s="17"/>
+      <c r="D48" s="18"/>
+      <c r="E48" s="18"/>
+      <c r="F48" s="17"/>
+      <c r="G48" s="19"/>
+      <c r="H48" s="19"/>
+      <c r="I48" s="19"/>
+      <c r="J48" s="21"/>
+      <c r="K48" s="22"/>
+    </row>
+    <row r="49" spans="2:11" ht="29.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B49" s="16"/>
+      <c r="C49" s="17"/>
+      <c r="D49" s="18"/>
+      <c r="E49" s="18"/>
+      <c r="F49" s="17"/>
+      <c r="G49" s="19"/>
+      <c r="H49" s="19"/>
+      <c r="I49" s="19"/>
+      <c r="J49" s="21"/>
+      <c r="K49" s="22"/>
+    </row>
+    <row r="50" spans="2:11" ht="29.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B50" s="16"/>
+      <c r="C50" s="17"/>
+      <c r="D50" s="18"/>
+      <c r="E50" s="18"/>
+      <c r="F50" s="17"/>
+      <c r="G50" s="19"/>
+      <c r="H50" s="19"/>
+      <c r="I50" s="19"/>
+      <c r="J50" s="21"/>
+      <c r="K50" s="22"/>
+    </row>
+    <row r="51" spans="2:11" ht="29.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B51" s="16"/>
+      <c r="C51" s="17"/>
+      <c r="D51" s="18"/>
+      <c r="E51" s="18"/>
+      <c r="F51" s="17"/>
+      <c r="G51" s="19"/>
+      <c r="H51" s="19"/>
+      <c r="I51" s="19"/>
+      <c r="J51" s="21"/>
+      <c r="K51" s="22"/>
+    </row>
+    <row r="52" spans="2:11" ht="29.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B52" s="16"/>
+      <c r="C52" s="17"/>
+      <c r="D52" s="18"/>
+      <c r="E52" s="18"/>
+      <c r="F52" s="17"/>
+      <c r="G52" s="19"/>
+      <c r="H52" s="19"/>
+      <c r="I52" s="19"/>
+      <c r="J52" s="21"/>
+      <c r="K52" s="22"/>
+    </row>
+    <row r="53" spans="2:11" ht="29.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B53" s="23"/>
+      <c r="C53" s="24" t="s">
+        <v>27</v>
+      </c>
+      <c r="D53" s="25"/>
+      <c r="E53" s="25"/>
+      <c r="F53" s="25"/>
+      <c r="G53" s="26"/>
+      <c r="H53" s="26"/>
+      <c r="I53" s="27"/>
+      <c r="J53" s="43">
+        <f>SUM(J14:J52)</f>
+      </c>
+      <c r="K53" s="28"/>
+    </row>
+    <row r="54" spans="2:11" ht="29.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B54" s="29"/>
+      <c r="C54" s="17"/>
+      <c r="D54" s="17"/>
+      <c r="E54" s="17"/>
+      <c r="F54" s="17"/>
+      <c r="G54" s="30"/>
+      <c r="H54" s="31"/>
+      <c r="I54" s="31"/>
+      <c r="J54" s="32"/>
+      <c r="K54" s="33"/>
+    </row>
+    <row r="55" spans="2:11" ht="29.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B55" s="29"/>
+      <c r="C55" s="17"/>
+      <c r="D55" s="17"/>
+      <c r="E55" s="17"/>
+      <c r="F55" s="17"/>
+      <c r="G55" s="30"/>
+      <c r="H55" s="31"/>
+      <c r="I55" s="31"/>
+      <c r="J55" s="32"/>
+      <c r="K55" s="33"/>
+    </row>
+    <row r="56" spans="2:11" ht="29.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B56" s="29"/>
+      <c r="C56" s="17"/>
+      <c r="D56" s="17"/>
+      <c r="E56" s="17"/>
+      <c r="F56" s="17"/>
+      <c r="G56" s="30"/>
+      <c r="H56" s="31"/>
+      <c r="I56" s="31"/>
+      <c r="J56" s="32"/>
+      <c r="K56" s="33"/>
+    </row>
+    <row r="57" spans="2:11" ht="29.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B57" s="14"/>
+      <c r="C57" s="9"/>
+      <c r="D57" s="9"/>
+      <c r="E57" s="9"/>
+      <c r="F57" s="9"/>
+      <c r="G57" s="10"/>
+      <c r="H57" s="11"/>
+      <c r="I57" s="11"/>
+      <c r="J57" s="12"/>
+      <c r="K57" s="15"/>
+    </row>
+    <row r="58" spans="2:11" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="B58" s="8"/>
+      <c r="C58" s="8"/>
+      <c r="D58" s="8"/>
+      <c r="E58" s="8"/>
+      <c r="F58" s="8"/>
+      <c r="G58" s="8"/>
+      <c r="H58" s="8"/>
+      <c r="I58" s="8"/>
+      <c r="J58" s="8"/>
+      <c r="K58" s="8"/>
     </row>
   </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="D8:D9"/>
-    <mergeCell ref="E8:E9"/>
-    <mergeCell ref="F8:F9"/>
-    <mergeCell ref="G8:H8"/>
-    <mergeCell ref="J8:J9"/>
+  <mergeCells count="9">
+    <mergeCell ref="J10:K10"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="D11:D12"/>
+    <mergeCell ref="E11:E12"/>
+    <mergeCell ref="F11:F12"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="K11:K12"/>
+    <mergeCell ref="I11:J11"/>
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="57" fitToHeight="0" orientation="portrait" r:id="rId1"/>
+  <pageMargins left="0.47244094488188981" right="0.43307086614173229" top="0.35433070866141736" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup paperSize="9" scale="40" orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
 </file>